--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822481</v>
+        <v>119822477</v>
       </c>
       <c r="B34" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474105</v>
+        <v>474098</v>
       </c>
       <c r="R34" t="n">
-        <v>7074062</v>
+        <v>7073885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,6 +4145,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822493</v>
+        <v>119822423</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474372</v>
+        <v>474482</v>
       </c>
       <c r="R35" t="n">
-        <v>7074297</v>
+        <v>7073717</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,6 +4252,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822477</v>
+        <v>119822481</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4289,21 +4299,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4313,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474098</v>
+        <v>474105</v>
       </c>
       <c r="R36" t="n">
-        <v>7073885</v>
+        <v>7074062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4349,11 +4359,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822423</v>
+        <v>119822493</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4396,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474482</v>
+        <v>474372</v>
       </c>
       <c r="R37" t="n">
-        <v>7073717</v>
+        <v>7074297</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4456,11 +4461,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822477</v>
+        <v>119822481</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474098</v>
+        <v>474105</v>
       </c>
       <c r="R34" t="n">
-        <v>7073885</v>
+        <v>7074062</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,11 +4145,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822423</v>
+        <v>119822493</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474482</v>
+        <v>474372</v>
       </c>
       <c r="R35" t="n">
-        <v>7073717</v>
+        <v>7074297</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4252,11 +4247,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,10 +4273,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822481</v>
+        <v>119822477</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,21 +4289,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4323,10 +4313,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474105</v>
+        <v>474098</v>
       </c>
       <c r="R36" t="n">
-        <v>7074062</v>
+        <v>7073885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4359,6 +4349,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,10 +4380,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822493</v>
+        <v>119822423</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4401,21 +4396,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474372</v>
+        <v>474482</v>
       </c>
       <c r="R37" t="n">
-        <v>7074297</v>
+        <v>7073717</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4461,6 +4456,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822490</v>
+        <v>119822420</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474005</v>
+        <v>474364</v>
       </c>
       <c r="R2" t="n">
-        <v>7073873</v>
+        <v>7073718</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822451</v>
+        <v>119822418</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474244</v>
+        <v>474133</v>
       </c>
       <c r="R3" t="n">
-        <v>7074159</v>
+        <v>7074227</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822469</v>
+        <v>119822437</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474129</v>
+        <v>474345</v>
       </c>
       <c r="R4" t="n">
-        <v>7074044</v>
+        <v>7074133</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822422</v>
+        <v>119822434</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474382</v>
+        <v>474317</v>
       </c>
       <c r="R5" t="n">
-        <v>7073703</v>
+        <v>7073906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822440</v>
+        <v>119822482</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474401</v>
+        <v>474095</v>
       </c>
       <c r="R6" t="n">
-        <v>7074148</v>
+        <v>7073945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822495</v>
+        <v>119822454</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474155</v>
+        <v>474182</v>
       </c>
       <c r="R7" t="n">
-        <v>7074201</v>
+        <v>7074153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822458</v>
+        <v>119822443</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474119</v>
+        <v>474450</v>
       </c>
       <c r="R8" t="n">
-        <v>7074246</v>
+        <v>7074166</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822441</v>
+        <v>119822492</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474422</v>
+        <v>474448</v>
       </c>
       <c r="R9" t="n">
-        <v>7074145</v>
+        <v>7074194</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822442</v>
+        <v>119822427</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474435</v>
+        <v>474530</v>
       </c>
       <c r="R11" t="n">
-        <v>7074155</v>
+        <v>7073855</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822489</v>
+        <v>119822468</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474517</v>
+        <v>474149</v>
       </c>
       <c r="R12" t="n">
-        <v>7073863</v>
+        <v>7074055</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822450</v>
+        <v>119822470</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474273</v>
+        <v>474150</v>
       </c>
       <c r="R13" t="n">
-        <v>7074232</v>
+        <v>7073954</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822455</v>
+        <v>119822432</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474172</v>
+        <v>474397</v>
       </c>
       <c r="R14" t="n">
-        <v>7074172</v>
+        <v>7073871</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822434</v>
+        <v>119822484</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474317</v>
+        <v>474078</v>
       </c>
       <c r="R15" t="n">
-        <v>7073906</v>
+        <v>7074201</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822454</v>
+        <v>119822474</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474182</v>
+        <v>474222</v>
       </c>
       <c r="R16" t="n">
-        <v>7074153</v>
+        <v>7073874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822476</v>
+        <v>119822438</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2300,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474209</v>
+        <v>474363</v>
       </c>
       <c r="R17" t="n">
-        <v>7073871</v>
+        <v>7074130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2335,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822456</v>
+        <v>119822462</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2407,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474160</v>
+        <v>474099</v>
       </c>
       <c r="R18" t="n">
-        <v>7074200</v>
+        <v>7074178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2442,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822427</v>
+        <v>119822481</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474530</v>
+        <v>474105</v>
       </c>
       <c r="R19" t="n">
-        <v>7073855</v>
+        <v>7074062</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,11 +2545,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822420</v>
+        <v>119822489</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474364</v>
+        <v>474517</v>
       </c>
       <c r="R20" t="n">
-        <v>7073718</v>
+        <v>7073863</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,11 +2647,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822475</v>
+        <v>119822430</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2728,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474205</v>
+        <v>474405</v>
       </c>
       <c r="R21" t="n">
-        <v>7073877</v>
+        <v>7073873</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2753,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2780,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822461</v>
+        <v>119822460</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2835,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474078</v>
+        <v>474092</v>
       </c>
       <c r="R22" t="n">
-        <v>7074226</v>
+        <v>7074245</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,7 +2887,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822446</v>
+        <v>119822439</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2942,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474395</v>
+        <v>474378</v>
       </c>
       <c r="R23" t="n">
-        <v>7074319</v>
+        <v>7074132</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2967,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,7 +2994,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822447</v>
+        <v>119822446</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3049,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474350</v>
+        <v>474395</v>
       </c>
       <c r="R24" t="n">
-        <v>7074246</v>
+        <v>7074319</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,7 +3101,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822425</v>
+        <v>119822442</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3156,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474571</v>
+        <v>474435</v>
       </c>
       <c r="R25" t="n">
-        <v>7073868</v>
+        <v>7074155</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822491</v>
+        <v>119822423</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3224,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474386</v>
+        <v>474482</v>
       </c>
       <c r="R26" t="n">
-        <v>7074137</v>
+        <v>7073717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,6 +3284,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,7 +3315,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822430</v>
+        <v>119822459</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3365,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474405</v>
+        <v>474109</v>
       </c>
       <c r="R27" t="n">
-        <v>7073873</v>
+        <v>7074246</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3395,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,7 +3422,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822445</v>
+        <v>119822447</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3472,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474457</v>
+        <v>474350</v>
       </c>
       <c r="R28" t="n">
-        <v>7074300</v>
+        <v>7074246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,7 +3529,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822463</v>
+        <v>119822478</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3579,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474097</v>
+        <v>474080</v>
       </c>
       <c r="R29" t="n">
-        <v>7074133</v>
+        <v>7073873</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3646,7 +3636,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822443</v>
+        <v>119822475</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3686,10 +3676,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474450</v>
+        <v>474205</v>
       </c>
       <c r="R30" t="n">
-        <v>7074166</v>
+        <v>7073877</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822482</v>
+        <v>119822449</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,21 +3759,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3793,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474095</v>
+        <v>474340</v>
       </c>
       <c r="R31" t="n">
-        <v>7073945</v>
+        <v>7074246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,6 +3819,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822449</v>
+        <v>119822466</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3895,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474340</v>
+        <v>474121</v>
       </c>
       <c r="R32" t="n">
-        <v>7074246</v>
+        <v>7074052</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,7 +3930,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822424</v>
+        <v>119822491</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,21 +3973,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474579</v>
+        <v>474386</v>
       </c>
       <c r="R33" t="n">
-        <v>7073758</v>
+        <v>7074137</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,11 +4033,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4059,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822481</v>
+        <v>119822452</v>
       </c>
       <c r="B34" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4075,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4099,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474105</v>
+        <v>474233</v>
       </c>
       <c r="R34" t="n">
-        <v>7074062</v>
+        <v>7074159</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,6 +4135,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,10 +4166,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822493</v>
+        <v>119822436</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4182,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4206,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474372</v>
+        <v>474298</v>
       </c>
       <c r="R35" t="n">
-        <v>7074297</v>
+        <v>7074026</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,6 +4242,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,7 +4273,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822477</v>
+        <v>119822429</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474098</v>
+        <v>474415</v>
       </c>
       <c r="R36" t="n">
-        <v>7073885</v>
+        <v>7073880</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822423</v>
+        <v>119822455</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474482</v>
+        <v>474172</v>
       </c>
       <c r="R37" t="n">
-        <v>7073717</v>
+        <v>7074172</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822438</v>
+        <v>119822433</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474363</v>
+        <v>474364</v>
       </c>
       <c r="R38" t="n">
-        <v>7074130</v>
+        <v>7073875</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4594,7 +4594,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822452</v>
+        <v>119822463</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474233</v>
+        <v>474097</v>
       </c>
       <c r="R39" t="n">
-        <v>7074159</v>
+        <v>7074133</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,10 +4701,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822457</v>
+        <v>119822488</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4717,21 +4717,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474128</v>
+        <v>474121</v>
       </c>
       <c r="R40" t="n">
-        <v>7074233</v>
+        <v>7073951</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4777,11 +4777,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4808,7 +4803,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822428</v>
+        <v>119822476</v>
       </c>
       <c r="B41" t="n">
         <v>57310</v>
@@ -4848,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474418</v>
+        <v>474209</v>
       </c>
       <c r="R41" t="n">
-        <v>7073882</v>
+        <v>7073871</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4915,7 +4910,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822419</v>
+        <v>119822453</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -4955,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474170</v>
+        <v>474191</v>
       </c>
       <c r="R42" t="n">
-        <v>7073676</v>
+        <v>7074152</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5022,7 +5017,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822471</v>
+        <v>119822445</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5062,10 +5057,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474127</v>
+        <v>474457</v>
       </c>
       <c r="R43" t="n">
-        <v>7073959</v>
+        <v>7074300</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5102,7 +5097,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,7 +5124,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822431</v>
+        <v>119822448</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5169,10 +5164,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474400</v>
+        <v>474334</v>
       </c>
       <c r="R44" t="n">
-        <v>7073871</v>
+        <v>7074241</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5236,7 +5231,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822448</v>
+        <v>119822456</v>
       </c>
       <c r="B45" t="n">
         <v>57310</v>
@@ -5276,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474334</v>
+        <v>474160</v>
       </c>
       <c r="R45" t="n">
-        <v>7074241</v>
+        <v>7074200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5316,7 +5311,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5343,7 +5338,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822478</v>
+        <v>119822424</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5383,10 +5378,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474080</v>
+        <v>474579</v>
       </c>
       <c r="R46" t="n">
-        <v>7073873</v>
+        <v>7073758</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5423,7 +5418,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5450,10 +5445,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822468</v>
+        <v>119822486</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5466,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5490,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474149</v>
+        <v>474121</v>
       </c>
       <c r="R47" t="n">
-        <v>7074055</v>
+        <v>7074098</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,11 +5521,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5557,7 +5547,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119822439</v>
+        <v>119822428</v>
       </c>
       <c r="B48" t="n">
         <v>57310</v>
@@ -5597,10 +5587,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474378</v>
+        <v>474418</v>
       </c>
       <c r="R48" t="n">
-        <v>7074132</v>
+        <v>7073882</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5637,7 +5627,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,7 +5654,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119822444</v>
+        <v>119822464</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5704,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474438</v>
+        <v>474094</v>
       </c>
       <c r="R49" t="n">
-        <v>7074241</v>
+        <v>7074062</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5744,7 +5734,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5771,7 +5761,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119822470</v>
+        <v>119822451</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5811,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474150</v>
+        <v>474244</v>
       </c>
       <c r="R50" t="n">
-        <v>7073954</v>
+        <v>7074159</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5851,7 +5841,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5878,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119822418</v>
+        <v>119822480</v>
       </c>
       <c r="B51" t="n">
-        <v>90562</v>
+        <v>79608</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5894,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474133</v>
+        <v>474098</v>
       </c>
       <c r="R51" t="n">
-        <v>7074227</v>
+        <v>7074059</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5980,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119822480</v>
+        <v>119822493</v>
       </c>
       <c r="B52" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5996,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6020,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474098</v>
+        <v>474372</v>
       </c>
       <c r="R52" t="n">
-        <v>7074059</v>
+        <v>7074297</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6082,10 +6072,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119822417</v>
+        <v>119822477</v>
       </c>
       <c r="B53" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6098,21 +6088,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6122,10 +6112,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474169</v>
+        <v>474098</v>
       </c>
       <c r="R53" t="n">
-        <v>7074185</v>
+        <v>7073885</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6158,6 +6148,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6184,7 +6179,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119822436</v>
+        <v>119822425</v>
       </c>
       <c r="B54" t="n">
         <v>57310</v>
@@ -6224,10 +6219,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474298</v>
+        <v>474571</v>
       </c>
       <c r="R54" t="n">
-        <v>7074026</v>
+        <v>7073868</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6264,7 +6259,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6291,10 +6286,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119822488</v>
+        <v>119822490</v>
       </c>
       <c r="B55" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6307,21 +6302,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6331,10 +6326,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474121</v>
+        <v>474005</v>
       </c>
       <c r="R55" t="n">
-        <v>7073951</v>
+        <v>7073873</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6393,10 +6388,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119822486</v>
+        <v>119822450</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6409,21 +6404,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6433,10 +6428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474121</v>
+        <v>474273</v>
       </c>
       <c r="R56" t="n">
-        <v>7074098</v>
+        <v>7074232</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6469,6 +6464,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6495,7 +6495,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119822460</v>
+        <v>119822461</v>
       </c>
       <c r="B57" t="n">
         <v>57310</v>
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474092</v>
+        <v>474078</v>
       </c>
       <c r="R57" t="n">
-        <v>7074245</v>
+        <v>7074226</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119822433</v>
+        <v>119822419</v>
       </c>
       <c r="B58" t="n">
         <v>57310</v>
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474364</v>
+        <v>474170</v>
       </c>
       <c r="R58" t="n">
-        <v>7073875</v>
+        <v>7073676</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6709,7 +6709,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119822453</v>
+        <v>119822457</v>
       </c>
       <c r="B59" t="n">
         <v>57310</v>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474191</v>
+        <v>474128</v>
       </c>
       <c r="R59" t="n">
-        <v>7074152</v>
+        <v>7074233</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6816,10 +6816,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119822484</v>
+        <v>119822441</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474078</v>
+        <v>474422</v>
       </c>
       <c r="R60" t="n">
-        <v>7074201</v>
+        <v>7074145</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,6 +6892,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6918,7 +6923,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119822432</v>
+        <v>119822422</v>
       </c>
       <c r="B61" t="n">
         <v>57310</v>
@@ -6958,10 +6963,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474397</v>
+        <v>474382</v>
       </c>
       <c r="R61" t="n">
-        <v>7073871</v>
+        <v>7073703</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7025,7 +7030,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119822462</v>
+        <v>119822440</v>
       </c>
       <c r="B62" t="n">
         <v>57310</v>
@@ -7065,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474099</v>
+        <v>474401</v>
       </c>
       <c r="R62" t="n">
-        <v>7074178</v>
+        <v>7074148</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7105,7 +7110,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7132,7 +7137,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119822437</v>
+        <v>119822458</v>
       </c>
       <c r="B63" t="n">
         <v>57310</v>
@@ -7172,10 +7177,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474345</v>
+        <v>474119</v>
       </c>
       <c r="R63" t="n">
-        <v>7074133</v>
+        <v>7074246</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7212,7 +7217,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7239,10 +7244,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119822464</v>
+        <v>119822485</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7255,21 +7260,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7279,10 +7284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474094</v>
+        <v>474136</v>
       </c>
       <c r="R64" t="n">
-        <v>7074062</v>
+        <v>7074108</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7315,11 +7320,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7346,10 +7346,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119822485</v>
+        <v>119822431</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7386,10 +7386,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474136</v>
+        <v>474400</v>
       </c>
       <c r="R65" t="n">
-        <v>7074108</v>
+        <v>7073871</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7422,6 +7422,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7448,7 +7453,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119822466</v>
+        <v>119822444</v>
       </c>
       <c r="B66" t="n">
         <v>57310</v>
@@ -7488,10 +7493,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474121</v>
+        <v>474438</v>
       </c>
       <c r="R66" t="n">
-        <v>7074052</v>
+        <v>7074241</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7555,7 +7560,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119822459</v>
+        <v>119822471</v>
       </c>
       <c r="B67" t="n">
         <v>57310</v>
@@ -7595,10 +7600,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474109</v>
+        <v>474127</v>
       </c>
       <c r="R67" t="n">
-        <v>7074246</v>
+        <v>7073959</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7635,7 +7640,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7662,7 +7667,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822467</v>
+        <v>119822469</v>
       </c>
       <c r="B68" t="n">
         <v>57310</v>
@@ -7702,10 +7707,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474148</v>
+        <v>474129</v>
       </c>
       <c r="R68" t="n">
-        <v>7074059</v>
+        <v>7074044</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7742,7 +7747,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7769,7 +7774,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822474</v>
+        <v>119822467</v>
       </c>
       <c r="B69" t="n">
         <v>57310</v>
@@ -7809,10 +7814,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474222</v>
+        <v>474148</v>
       </c>
       <c r="R69" t="n">
-        <v>7073874</v>
+        <v>7074059</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7849,7 +7854,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7876,10 +7881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119822492</v>
+        <v>119822417</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7892,21 +7897,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7916,10 +7921,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474448</v>
+        <v>474169</v>
       </c>
       <c r="R70" t="n">
-        <v>7074194</v>
+        <v>7074185</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7978,10 +7983,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119822429</v>
+        <v>119822495</v>
       </c>
       <c r="B71" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7994,21 +7999,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8018,10 +8023,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474415</v>
+        <v>474155</v>
       </c>
       <c r="R71" t="n">
-        <v>7073880</v>
+        <v>7074201</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8054,11 +8059,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -3743,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822449</v>
+        <v>119822491</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3759,21 +3759,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474340</v>
+        <v>474386</v>
       </c>
       <c r="R31" t="n">
-        <v>7074246</v>
+        <v>7074137</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3819,11 +3819,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3850,7 +3845,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822466</v>
+        <v>119822449</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3890,10 +3885,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474121</v>
+        <v>474340</v>
       </c>
       <c r="R32" t="n">
-        <v>7074052</v>
+        <v>7074246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3930,7 +3925,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,10 +3952,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822491</v>
+        <v>119822466</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3973,21 +3968,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474386</v>
+        <v>474121</v>
       </c>
       <c r="R33" t="n">
-        <v>7074137</v>
+        <v>7074052</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4033,6 +4028,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5445,10 +5445,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822486</v>
+        <v>119822428</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474121</v>
+        <v>474418</v>
       </c>
       <c r="R47" t="n">
-        <v>7074098</v>
+        <v>7073882</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5521,6 +5521,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5547,7 +5552,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119822428</v>
+        <v>119822464</v>
       </c>
       <c r="B48" t="n">
         <v>57310</v>
@@ -5587,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474418</v>
+        <v>474094</v>
       </c>
       <c r="R48" t="n">
-        <v>7073882</v>
+        <v>7074062</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5627,7 +5632,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5654,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119822464</v>
+        <v>119822486</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5670,21 +5675,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474094</v>
+        <v>474121</v>
       </c>
       <c r="R49" t="n">
-        <v>7074062</v>
+        <v>7074098</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5730,11 +5735,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5970,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119822493</v>
+        <v>119822477</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474372</v>
+        <v>474098</v>
       </c>
       <c r="R52" t="n">
-        <v>7074297</v>
+        <v>7073885</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6046,6 +6046,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6072,7 +6077,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119822477</v>
+        <v>119822425</v>
       </c>
       <c r="B53" t="n">
         <v>57310</v>
@@ -6112,10 +6117,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474098</v>
+        <v>474571</v>
       </c>
       <c r="R53" t="n">
-        <v>7073885</v>
+        <v>7073868</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6179,10 +6184,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119822425</v>
+        <v>119822493</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6195,21 +6200,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6219,10 +6224,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474571</v>
+        <v>474372</v>
       </c>
       <c r="R54" t="n">
-        <v>7073868</v>
+        <v>7074297</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6255,11 +6260,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6816,7 +6816,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119822441</v>
+        <v>119822458</v>
       </c>
       <c r="B60" t="n">
         <v>57310</v>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474422</v>
+        <v>474119</v>
       </c>
       <c r="R60" t="n">
-        <v>7074145</v>
+        <v>7074246</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119822422</v>
+        <v>119822441</v>
       </c>
       <c r="B61" t="n">
         <v>57310</v>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474382</v>
+        <v>474422</v>
       </c>
       <c r="R61" t="n">
-        <v>7073703</v>
+        <v>7074145</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7030,7 +7030,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119822440</v>
+        <v>119822422</v>
       </c>
       <c r="B62" t="n">
         <v>57310</v>
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474401</v>
+        <v>474382</v>
       </c>
       <c r="R62" t="n">
-        <v>7074148</v>
+        <v>7073703</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7137,7 +7137,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119822458</v>
+        <v>119822440</v>
       </c>
       <c r="B63" t="n">
         <v>57310</v>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474119</v>
+        <v>474401</v>
       </c>
       <c r="R63" t="n">
-        <v>7074246</v>
+        <v>7074148</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7667,10 +7667,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822469</v>
+        <v>119822417</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7683,21 +7683,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474129</v>
+        <v>474169</v>
       </c>
       <c r="R68" t="n">
-        <v>7074044</v>
+        <v>7074185</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7743,11 +7743,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7774,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822467</v>
+        <v>119822495</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7790,21 +7785,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7814,10 +7809,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474148</v>
+        <v>474155</v>
       </c>
       <c r="R69" t="n">
-        <v>7074059</v>
+        <v>7074201</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7850,11 +7845,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7881,10 +7871,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119822417</v>
+        <v>119822469</v>
       </c>
       <c r="B70" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7897,21 +7887,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7921,10 +7911,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474169</v>
+        <v>474129</v>
       </c>
       <c r="R70" t="n">
-        <v>7074185</v>
+        <v>7074044</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7957,6 +7947,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7983,10 +7978,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119822495</v>
+        <v>119822467</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7999,21 +7994,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8023,10 +8018,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474155</v>
+        <v>474148</v>
       </c>
       <c r="R71" t="n">
-        <v>7074201</v>
+        <v>7074059</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8059,6 +8054,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822420</v>
+        <v>119822451</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474364</v>
+        <v>474244</v>
       </c>
       <c r="R2" t="n">
-        <v>7073718</v>
+        <v>7074159</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822418</v>
+        <v>119822441</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474133</v>
+        <v>474422</v>
       </c>
       <c r="R3" t="n">
-        <v>7074227</v>
+        <v>7074145</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822437</v>
+        <v>119822448</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474345</v>
+        <v>474334</v>
       </c>
       <c r="R4" t="n">
-        <v>7074133</v>
+        <v>7074241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822434</v>
+        <v>119822492</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474317</v>
+        <v>474448</v>
       </c>
       <c r="R5" t="n">
-        <v>7073906</v>
+        <v>7074194</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822482</v>
+        <v>119822468</v>
       </c>
       <c r="B6" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474095</v>
+        <v>474149</v>
       </c>
       <c r="R6" t="n">
-        <v>7073945</v>
+        <v>7074055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822454</v>
+        <v>119822476</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474182</v>
+        <v>474209</v>
       </c>
       <c r="R7" t="n">
-        <v>7074153</v>
+        <v>7073871</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822443</v>
+        <v>119822436</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474450</v>
+        <v>474298</v>
       </c>
       <c r="R8" t="n">
-        <v>7074166</v>
+        <v>7074026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822492</v>
+        <v>119822462</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474448</v>
+        <v>474099</v>
       </c>
       <c r="R9" t="n">
-        <v>7074194</v>
+        <v>7074178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822494</v>
+        <v>119822463</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474330</v>
+        <v>474097</v>
       </c>
       <c r="R10" t="n">
-        <v>7074260</v>
+        <v>7074133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822427</v>
+        <v>119822480</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474530</v>
+        <v>474098</v>
       </c>
       <c r="R11" t="n">
-        <v>7073855</v>
+        <v>7074059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822468</v>
+        <v>119822454</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1765,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474149</v>
+        <v>474182</v>
       </c>
       <c r="R12" t="n">
-        <v>7074055</v>
+        <v>7074153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822470</v>
+        <v>119822458</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1872,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474150</v>
+        <v>474119</v>
       </c>
       <c r="R13" t="n">
-        <v>7073954</v>
+        <v>7074246</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822432</v>
+        <v>119822466</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1979,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474397</v>
+        <v>474121</v>
       </c>
       <c r="R14" t="n">
-        <v>7073871</v>
+        <v>7074052</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822484</v>
+        <v>119822419</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474078</v>
+        <v>474170</v>
       </c>
       <c r="R15" t="n">
-        <v>7074201</v>
+        <v>7073676</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822474</v>
+        <v>119822422</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2188,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474222</v>
+        <v>474382</v>
       </c>
       <c r="R16" t="n">
-        <v>7073874</v>
+        <v>7073703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822438</v>
+        <v>119822459</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2295,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474363</v>
+        <v>474109</v>
       </c>
       <c r="R17" t="n">
-        <v>7074130</v>
+        <v>7074246</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822462</v>
+        <v>119822490</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474099</v>
+        <v>474005</v>
       </c>
       <c r="R18" t="n">
-        <v>7074178</v>
+        <v>7073873</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,11 +2453,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822481</v>
+        <v>119822425</v>
       </c>
       <c r="B19" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474105</v>
+        <v>474571</v>
       </c>
       <c r="R19" t="n">
-        <v>7074062</v>
+        <v>7073868</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822489</v>
+        <v>119822471</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474517</v>
+        <v>474127</v>
       </c>
       <c r="R20" t="n">
-        <v>7073863</v>
+        <v>7073959</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822430</v>
+        <v>119822482</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474405</v>
+        <v>474095</v>
       </c>
       <c r="R21" t="n">
-        <v>7073873</v>
+        <v>7073945</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,11 +2769,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822460</v>
+        <v>119822477</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2820,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474092</v>
+        <v>474098</v>
       </c>
       <c r="R22" t="n">
-        <v>7074245</v>
+        <v>7073885</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822439</v>
+        <v>119822424</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2927,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474378</v>
+        <v>474579</v>
       </c>
       <c r="R23" t="n">
-        <v>7074132</v>
+        <v>7073758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2967,7 +2982,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822446</v>
+        <v>119822475</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3034,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474395</v>
+        <v>474205</v>
       </c>
       <c r="R24" t="n">
-        <v>7074319</v>
+        <v>7073877</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822442</v>
+        <v>119822485</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474435</v>
+        <v>474136</v>
       </c>
       <c r="R25" t="n">
-        <v>7074155</v>
+        <v>7074108</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3177,11 +3192,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3208,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822423</v>
+        <v>119822452</v>
       </c>
       <c r="B26" t="n">
         <v>57310</v>
@@ -3248,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474482</v>
+        <v>474233</v>
       </c>
       <c r="R26" t="n">
-        <v>7073717</v>
+        <v>7074159</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3288,7 +3298,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3315,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822459</v>
+        <v>119822427</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3355,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474109</v>
+        <v>474530</v>
       </c>
       <c r="R27" t="n">
-        <v>7074246</v>
+        <v>7073855</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,7 +3432,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822447</v>
+        <v>119822474</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3462,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474350</v>
+        <v>474222</v>
       </c>
       <c r="R28" t="n">
-        <v>7074246</v>
+        <v>7073874</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3502,7 +3512,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3529,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822478</v>
+        <v>119822453</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3569,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474080</v>
+        <v>474191</v>
       </c>
       <c r="R29" t="n">
-        <v>7073873</v>
+        <v>7074152</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3636,10 +3646,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822475</v>
+        <v>119822494</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3652,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474205</v>
+        <v>474330</v>
       </c>
       <c r="R30" t="n">
-        <v>7073877</v>
+        <v>7074260</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,11 +3722,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822491</v>
+        <v>119822449</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3759,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3783,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474386</v>
+        <v>474340</v>
       </c>
       <c r="R31" t="n">
-        <v>7074137</v>
+        <v>7074246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3819,6 +3824,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822449</v>
+        <v>119822447</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3885,7 +3895,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474340</v>
+        <v>474350</v>
       </c>
       <c r="R32" t="n">
         <v>7074246</v>
@@ -3952,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822466</v>
+        <v>119822417</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3968,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474121</v>
+        <v>474169</v>
       </c>
       <c r="R33" t="n">
-        <v>7074052</v>
+        <v>7074185</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4028,11 +4038,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4059,7 +4064,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822452</v>
+        <v>119822423</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4099,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474233</v>
+        <v>474482</v>
       </c>
       <c r="R34" t="n">
-        <v>7074159</v>
+        <v>7073717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4139,7 +4144,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,7 +4171,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822436</v>
+        <v>119822420</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4206,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474298</v>
+        <v>474364</v>
       </c>
       <c r="R35" t="n">
-        <v>7074026</v>
+        <v>7073718</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4246,7 +4251,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822429</v>
+        <v>119822478</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4313,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474415</v>
+        <v>474080</v>
       </c>
       <c r="R36" t="n">
-        <v>7073880</v>
+        <v>7073873</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4380,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822455</v>
+        <v>119822489</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4396,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474172</v>
+        <v>474517</v>
       </c>
       <c r="R37" t="n">
-        <v>7074172</v>
+        <v>7073863</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4456,11 +4461,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4487,10 +4487,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822433</v>
+        <v>119822488</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4503,21 +4503,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474364</v>
+        <v>474121</v>
       </c>
       <c r="R38" t="n">
-        <v>7073875</v>
+        <v>7073951</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4563,11 +4563,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4594,7 +4589,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822463</v>
+        <v>119822469</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4634,10 +4629,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474097</v>
+        <v>474129</v>
       </c>
       <c r="R39" t="n">
-        <v>7074133</v>
+        <v>7074044</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4674,7 +4669,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4701,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822488</v>
+        <v>119822434</v>
       </c>
       <c r="B40" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4717,21 +4712,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4741,10 +4736,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474121</v>
+        <v>474317</v>
       </c>
       <c r="R40" t="n">
-        <v>7073951</v>
+        <v>7073906</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4777,6 +4772,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4803,7 +4803,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822476</v>
+        <v>119822470</v>
       </c>
       <c r="B41" t="n">
         <v>57310</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474209</v>
+        <v>474150</v>
       </c>
       <c r="R41" t="n">
-        <v>7073871</v>
+        <v>7073954</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4910,7 +4910,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822453</v>
+        <v>119822432</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474191</v>
+        <v>474397</v>
       </c>
       <c r="R42" t="n">
-        <v>7074152</v>
+        <v>7073871</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5017,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822445</v>
+        <v>119822437</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474457</v>
+        <v>474345</v>
       </c>
       <c r="R43" t="n">
-        <v>7074300</v>
+        <v>7074133</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5124,7 +5124,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822448</v>
+        <v>119822440</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474334</v>
+        <v>474401</v>
       </c>
       <c r="R44" t="n">
-        <v>7074241</v>
+        <v>7074148</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822456</v>
+        <v>119822491</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474160</v>
+        <v>474386</v>
       </c>
       <c r="R45" t="n">
-        <v>7074200</v>
+        <v>7074137</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5307,11 +5307,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5338,7 +5333,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822424</v>
+        <v>119822430</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5378,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474579</v>
+        <v>474405</v>
       </c>
       <c r="R46" t="n">
-        <v>7073758</v>
+        <v>7073873</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5418,7 +5413,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5445,7 +5440,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822428</v>
+        <v>119822438</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474418</v>
+        <v>474363</v>
       </c>
       <c r="R47" t="n">
-        <v>7073882</v>
+        <v>7074130</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5525,7 +5520,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5552,7 +5547,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119822464</v>
+        <v>119822461</v>
       </c>
       <c r="B48" t="n">
         <v>57310</v>
@@ -5592,10 +5587,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474094</v>
+        <v>474078</v>
       </c>
       <c r="R48" t="n">
-        <v>7074062</v>
+        <v>7074226</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5632,7 +5627,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,10 +5654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119822486</v>
+        <v>119822428</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5675,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5699,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474121</v>
+        <v>474418</v>
       </c>
       <c r="R49" t="n">
-        <v>7074098</v>
+        <v>7073882</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5735,6 +5730,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5761,7 +5761,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119822451</v>
+        <v>119822456</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474244</v>
+        <v>474160</v>
       </c>
       <c r="R50" t="n">
-        <v>7074159</v>
+        <v>7074200</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5868,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119822480</v>
+        <v>119822457</v>
       </c>
       <c r="B51" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474098</v>
+        <v>474128</v>
       </c>
       <c r="R51" t="n">
-        <v>7074059</v>
+        <v>7074233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5944,6 +5944,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119822477</v>
+        <v>119822493</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5986,21 +5991,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474098</v>
+        <v>474372</v>
       </c>
       <c r="R52" t="n">
-        <v>7073885</v>
+        <v>7074297</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6046,11 +6051,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6077,7 +6077,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119822425</v>
+        <v>119822464</v>
       </c>
       <c r="B53" t="n">
         <v>57310</v>
@@ -6117,10 +6117,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474571</v>
+        <v>474094</v>
       </c>
       <c r="R53" t="n">
-        <v>7073868</v>
+        <v>7074062</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6184,10 +6184,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119822493</v>
+        <v>119822431</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6200,21 +6200,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474372</v>
+        <v>474400</v>
       </c>
       <c r="R54" t="n">
-        <v>7074297</v>
+        <v>7073871</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6260,6 +6260,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6286,10 +6291,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119822490</v>
+        <v>119822444</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6302,21 +6307,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6326,10 +6331,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474005</v>
+        <v>474438</v>
       </c>
       <c r="R55" t="n">
-        <v>7073873</v>
+        <v>7074241</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6362,6 +6367,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6388,7 +6398,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119822450</v>
+        <v>119822455</v>
       </c>
       <c r="B56" t="n">
         <v>57310</v>
@@ -6428,10 +6438,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474273</v>
+        <v>474172</v>
       </c>
       <c r="R56" t="n">
-        <v>7074232</v>
+        <v>7074172</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6468,7 +6478,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6495,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119822461</v>
+        <v>119822486</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6511,21 +6521,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6535,10 +6545,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474078</v>
+        <v>474121</v>
       </c>
       <c r="R57" t="n">
-        <v>7074226</v>
+        <v>7074098</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6571,11 +6581,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6602,10 +6607,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119822419</v>
+        <v>119822481</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6618,21 +6623,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6642,10 +6647,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474170</v>
+        <v>474105</v>
       </c>
       <c r="R58" t="n">
-        <v>7073676</v>
+        <v>7074062</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6678,11 +6683,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6709,7 +6709,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119822457</v>
+        <v>119822439</v>
       </c>
       <c r="B59" t="n">
         <v>57310</v>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474128</v>
+        <v>474378</v>
       </c>
       <c r="R59" t="n">
-        <v>7074233</v>
+        <v>7074132</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6816,10 +6816,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119822458</v>
+        <v>119822418</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474119</v>
+        <v>474133</v>
       </c>
       <c r="R60" t="n">
-        <v>7074246</v>
+        <v>7074227</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,11 +6892,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6923,7 +6918,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119822441</v>
+        <v>119822460</v>
       </c>
       <c r="B61" t="n">
         <v>57310</v>
@@ -6963,10 +6958,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474422</v>
+        <v>474092</v>
       </c>
       <c r="R61" t="n">
-        <v>7074145</v>
+        <v>7074245</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7030,10 +7025,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119822422</v>
+        <v>119822484</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7046,21 +7041,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7070,10 +7065,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474382</v>
+        <v>474078</v>
       </c>
       <c r="R62" t="n">
-        <v>7073703</v>
+        <v>7074201</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7106,11 +7101,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7137,7 +7127,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119822440</v>
+        <v>119822429</v>
       </c>
       <c r="B63" t="n">
         <v>57310</v>
@@ -7177,10 +7167,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474401</v>
+        <v>474415</v>
       </c>
       <c r="R63" t="n">
-        <v>7074148</v>
+        <v>7073880</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7244,10 +7234,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119822485</v>
+        <v>119822442</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7260,21 +7250,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7284,10 +7274,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474136</v>
+        <v>474435</v>
       </c>
       <c r="R64" t="n">
-        <v>7074108</v>
+        <v>7074155</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7320,6 +7310,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7346,7 +7341,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119822431</v>
+        <v>119822467</v>
       </c>
       <c r="B65" t="n">
         <v>57310</v>
@@ -7386,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474400</v>
+        <v>474148</v>
       </c>
       <c r="R65" t="n">
-        <v>7073871</v>
+        <v>7074059</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7426,7 +7421,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7453,7 +7448,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119822444</v>
+        <v>119822433</v>
       </c>
       <c r="B66" t="n">
         <v>57310</v>
@@ -7493,10 +7488,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474438</v>
+        <v>474364</v>
       </c>
       <c r="R66" t="n">
-        <v>7074241</v>
+        <v>7073875</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7533,7 +7528,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7560,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119822471</v>
+        <v>119822495</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7576,21 +7571,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7600,10 +7595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474127</v>
+        <v>474155</v>
       </c>
       <c r="R67" t="n">
-        <v>7073959</v>
+        <v>7074201</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7636,11 +7631,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7667,10 +7657,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822417</v>
+        <v>119822446</v>
       </c>
       <c r="B68" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7683,21 +7673,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7707,10 +7697,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474169</v>
+        <v>474395</v>
       </c>
       <c r="R68" t="n">
-        <v>7074185</v>
+        <v>7074319</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7743,6 +7733,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7769,10 +7764,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822495</v>
+        <v>119822443</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7785,21 +7780,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7809,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474155</v>
+        <v>474450</v>
       </c>
       <c r="R69" t="n">
-        <v>7074201</v>
+        <v>7074166</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7845,6 +7840,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7871,7 +7871,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119822469</v>
+        <v>119822450</v>
       </c>
       <c r="B70" t="n">
         <v>57310</v>
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474129</v>
+        <v>474273</v>
       </c>
       <c r="R70" t="n">
-        <v>7074044</v>
+        <v>7074232</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119822467</v>
+        <v>119822445</v>
       </c>
       <c r="B71" t="n">
         <v>57310</v>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474148</v>
+        <v>474457</v>
       </c>
       <c r="R71" t="n">
-        <v>7074059</v>
+        <v>7074300</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822476</v>
+        <v>119822436</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474209</v>
+        <v>474298</v>
       </c>
       <c r="R7" t="n">
-        <v>7073871</v>
+        <v>7074026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822436</v>
+        <v>119822476</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474298</v>
+        <v>474209</v>
       </c>
       <c r="R8" t="n">
-        <v>7074026</v>
+        <v>7073871</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822480</v>
+        <v>119822454</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474098</v>
+        <v>474182</v>
       </c>
       <c r="R11" t="n">
-        <v>7074059</v>
+        <v>7074153</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822454</v>
+        <v>119822458</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474182</v>
+        <v>474119</v>
       </c>
       <c r="R12" t="n">
-        <v>7074153</v>
+        <v>7074246</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822458</v>
+        <v>119822466</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474119</v>
+        <v>474121</v>
       </c>
       <c r="R13" t="n">
-        <v>7074246</v>
+        <v>7074052</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822466</v>
+        <v>119822480</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474121</v>
+        <v>474098</v>
       </c>
       <c r="R14" t="n">
-        <v>7074052</v>
+        <v>7074059</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822489</v>
+        <v>119822488</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4401,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474517</v>
+        <v>474121</v>
       </c>
       <c r="R37" t="n">
-        <v>7073863</v>
+        <v>7073951</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,10 +4487,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822488</v>
+        <v>119822469</v>
       </c>
       <c r="B38" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4503,21 +4503,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474121</v>
+        <v>474129</v>
       </c>
       <c r="R38" t="n">
-        <v>7073951</v>
+        <v>7074044</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4563,6 +4563,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4589,7 +4594,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822469</v>
+        <v>119822434</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4629,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474129</v>
+        <v>474317</v>
       </c>
       <c r="R39" t="n">
-        <v>7074044</v>
+        <v>7073906</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,7 +4674,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4696,7 +4701,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822434</v>
+        <v>119822470</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4736,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474317</v>
+        <v>474150</v>
       </c>
       <c r="R40" t="n">
-        <v>7073906</v>
+        <v>7073954</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4776,7 +4781,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4803,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822470</v>
+        <v>119822489</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4819,21 +4824,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4843,10 +4848,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474150</v>
+        <v>474517</v>
       </c>
       <c r="R41" t="n">
-        <v>7073954</v>
+        <v>7073863</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4879,11 +4884,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4910,7 +4910,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822432</v>
+        <v>119822430</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474397</v>
+        <v>474405</v>
       </c>
       <c r="R42" t="n">
-        <v>7073871</v>
+        <v>7073873</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5017,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822437</v>
+        <v>119822438</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474345</v>
+        <v>474363</v>
       </c>
       <c r="R43" t="n">
-        <v>7074133</v>
+        <v>7074130</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5124,7 +5124,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822440</v>
+        <v>119822461</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474401</v>
+        <v>474078</v>
       </c>
       <c r="R44" t="n">
-        <v>7074148</v>
+        <v>7074226</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822491</v>
+        <v>119822428</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474386</v>
+        <v>474418</v>
       </c>
       <c r="R45" t="n">
-        <v>7074137</v>
+        <v>7073882</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5307,6 +5307,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5333,7 +5338,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822430</v>
+        <v>119822432</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5373,10 +5378,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474405</v>
+        <v>474397</v>
       </c>
       <c r="R46" t="n">
-        <v>7073873</v>
+        <v>7073871</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,7 +5418,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5440,7 +5445,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822438</v>
+        <v>119822456</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474363</v>
+        <v>474160</v>
       </c>
       <c r="R47" t="n">
-        <v>7074130</v>
+        <v>7074200</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5520,7 +5525,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5547,7 +5552,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119822461</v>
+        <v>119822437</v>
       </c>
       <c r="B48" t="n">
         <v>57310</v>
@@ -5587,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474078</v>
+        <v>474345</v>
       </c>
       <c r="R48" t="n">
-        <v>7074226</v>
+        <v>7074133</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5627,7 +5632,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5654,7 +5659,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119822428</v>
+        <v>119822457</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5694,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474418</v>
+        <v>474128</v>
       </c>
       <c r="R49" t="n">
-        <v>7073882</v>
+        <v>7074233</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,7 +5766,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119822456</v>
+        <v>119822440</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5801,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474160</v>
+        <v>474401</v>
       </c>
       <c r="R50" t="n">
-        <v>7074200</v>
+        <v>7074148</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5868,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119822457</v>
+        <v>119822491</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5889,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474128</v>
+        <v>474386</v>
       </c>
       <c r="R51" t="n">
-        <v>7074233</v>
+        <v>7074137</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5944,11 +5949,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119822493</v>
+        <v>119822431</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5991,21 +5991,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474372</v>
+        <v>474400</v>
       </c>
       <c r="R52" t="n">
-        <v>7074297</v>
+        <v>7073871</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6051,6 +6051,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6184,7 +6189,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119822431</v>
+        <v>119822444</v>
       </c>
       <c r="B54" t="n">
         <v>57310</v>
@@ -6224,10 +6229,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474400</v>
+        <v>474438</v>
       </c>
       <c r="R54" t="n">
-        <v>7073871</v>
+        <v>7074241</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6291,10 +6296,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119822444</v>
+        <v>119822493</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6307,21 +6312,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6331,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474438</v>
+        <v>474372</v>
       </c>
       <c r="R55" t="n">
-        <v>7074241</v>
+        <v>7074297</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6367,11 +6372,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6398,10 +6398,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119822455</v>
+        <v>119822486</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6414,21 +6414,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6438,10 +6438,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474172</v>
+        <v>474121</v>
       </c>
       <c r="R56" t="n">
-        <v>7074172</v>
+        <v>7074098</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6474,11 +6474,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6505,10 +6500,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119822486</v>
+        <v>119822455</v>
       </c>
       <c r="B57" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6521,21 +6516,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6545,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474121</v>
+        <v>474172</v>
       </c>
       <c r="R57" t="n">
-        <v>7074098</v>
+        <v>7074172</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6581,6 +6576,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822451</v>
+        <v>119822492</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474244</v>
+        <v>474448</v>
       </c>
       <c r="R2" t="n">
-        <v>7074159</v>
+        <v>7074194</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822441</v>
+        <v>119822419</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474422</v>
+        <v>474170</v>
       </c>
       <c r="R3" t="n">
-        <v>7074145</v>
+        <v>7073676</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822448</v>
+        <v>119822442</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474334</v>
+        <v>474435</v>
       </c>
       <c r="R4" t="n">
-        <v>7074241</v>
+        <v>7074155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822492</v>
+        <v>119822481</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474448</v>
+        <v>474105</v>
       </c>
       <c r="R5" t="n">
-        <v>7074194</v>
+        <v>7074062</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822468</v>
+        <v>119822461</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474149</v>
+        <v>474078</v>
       </c>
       <c r="R6" t="n">
-        <v>7074055</v>
+        <v>7074226</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822436</v>
+        <v>119822439</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474298</v>
+        <v>474378</v>
       </c>
       <c r="R7" t="n">
-        <v>7074026</v>
+        <v>7074132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822476</v>
+        <v>119822478</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474209</v>
+        <v>474080</v>
       </c>
       <c r="R8" t="n">
-        <v>7073871</v>
+        <v>7073873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822462</v>
+        <v>119822493</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474099</v>
+        <v>474372</v>
       </c>
       <c r="R9" t="n">
-        <v>7074178</v>
+        <v>7074297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822463</v>
+        <v>119822494</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474097</v>
+        <v>474330</v>
       </c>
       <c r="R10" t="n">
-        <v>7074133</v>
+        <v>7074260</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822454</v>
+        <v>119822467</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1673,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474182</v>
+        <v>474148</v>
       </c>
       <c r="R11" t="n">
-        <v>7074153</v>
+        <v>7074059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822458</v>
+        <v>119822453</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1780,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474119</v>
+        <v>474191</v>
       </c>
       <c r="R12" t="n">
-        <v>7074246</v>
+        <v>7074152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822466</v>
+        <v>119822482</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474121</v>
+        <v>474095</v>
       </c>
       <c r="R13" t="n">
-        <v>7074052</v>
+        <v>7073945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822419</v>
+        <v>119822428</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2096,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474170</v>
+        <v>474418</v>
       </c>
       <c r="R15" t="n">
-        <v>7073676</v>
+        <v>7073882</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,7 +2143,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822422</v>
+        <v>119822425</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2203,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474382</v>
+        <v>474571</v>
       </c>
       <c r="R16" t="n">
-        <v>7073703</v>
+        <v>7073868</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2223,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822459</v>
+        <v>119822471</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2310,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474109</v>
+        <v>474127</v>
       </c>
       <c r="R17" t="n">
-        <v>7074246</v>
+        <v>7073959</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2330,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822490</v>
+        <v>119822430</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2373,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,7 +2397,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474005</v>
+        <v>474405</v>
       </c>
       <c r="R18" t="n">
         <v>7073873</v>
@@ -2453,6 +2433,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822425</v>
+        <v>119822438</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2519,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474571</v>
+        <v>474363</v>
       </c>
       <c r="R19" t="n">
-        <v>7073868</v>
+        <v>7074130</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2544,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822471</v>
+        <v>119822456</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2626,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474127</v>
+        <v>474160</v>
       </c>
       <c r="R20" t="n">
-        <v>7073959</v>
+        <v>7074200</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2651,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822482</v>
+        <v>119822463</v>
       </c>
       <c r="B21" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474095</v>
+        <v>474097</v>
       </c>
       <c r="R21" t="n">
-        <v>7073945</v>
+        <v>7074133</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,6 +2754,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822477</v>
+        <v>119822423</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2835,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474098</v>
+        <v>474482</v>
       </c>
       <c r="R22" t="n">
-        <v>7073885</v>
+        <v>7073717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2865,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,7 +2892,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822424</v>
+        <v>119822431</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2942,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474579</v>
+        <v>474400</v>
       </c>
       <c r="R23" t="n">
-        <v>7073758</v>
+        <v>7073871</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,7 +2999,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822475</v>
+        <v>119822437</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3049,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474205</v>
+        <v>474345</v>
       </c>
       <c r="R24" t="n">
-        <v>7073877</v>
+        <v>7074133</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3079,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822485</v>
+        <v>119822457</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3122,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474136</v>
+        <v>474128</v>
       </c>
       <c r="R25" t="n">
-        <v>7074108</v>
+        <v>7074233</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,6 +3182,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822452</v>
+        <v>119822446</v>
       </c>
       <c r="B26" t="n">
         <v>57310</v>
@@ -3258,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474233</v>
+        <v>474395</v>
       </c>
       <c r="R26" t="n">
-        <v>7074159</v>
+        <v>7074319</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822427</v>
+        <v>119822452</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474530</v>
+        <v>474233</v>
       </c>
       <c r="R27" t="n">
-        <v>7073855</v>
+        <v>7074159</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3432,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822474</v>
+        <v>119822450</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474222</v>
+        <v>474273</v>
       </c>
       <c r="R28" t="n">
-        <v>7073874</v>
+        <v>7074232</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3507,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822453</v>
+        <v>119822436</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3579,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474191</v>
+        <v>474298</v>
       </c>
       <c r="R29" t="n">
-        <v>7074152</v>
+        <v>7074026</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822494</v>
+        <v>119822432</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3662,21 +3657,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3686,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474330</v>
+        <v>474397</v>
       </c>
       <c r="R30" t="n">
-        <v>7074260</v>
+        <v>7073871</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3722,6 +3717,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822449</v>
+        <v>119822491</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474340</v>
+        <v>474386</v>
       </c>
       <c r="R31" t="n">
-        <v>7074246</v>
+        <v>7074137</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,11 +3824,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822447</v>
+        <v>119822451</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3895,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474350</v>
+        <v>474244</v>
       </c>
       <c r="R32" t="n">
-        <v>7074246</v>
+        <v>7074159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822417</v>
+        <v>119822462</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,21 +3973,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474169</v>
+        <v>474099</v>
       </c>
       <c r="R33" t="n">
-        <v>7074185</v>
+        <v>7074178</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,6 +4033,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,7 +4064,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822423</v>
+        <v>119822464</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474482</v>
+        <v>474094</v>
       </c>
       <c r="R34" t="n">
-        <v>7073717</v>
+        <v>7074062</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,7 +4171,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822420</v>
+        <v>119822468</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474364</v>
+        <v>474149</v>
       </c>
       <c r="R35" t="n">
-        <v>7073718</v>
+        <v>7074055</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822478</v>
+        <v>119822422</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474080</v>
+        <v>474382</v>
       </c>
       <c r="R36" t="n">
-        <v>7073873</v>
+        <v>7073703</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822488</v>
+        <v>119822449</v>
       </c>
       <c r="B37" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4401,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474121</v>
+        <v>474340</v>
       </c>
       <c r="R37" t="n">
-        <v>7073951</v>
+        <v>7074246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4461,6 +4461,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4487,7 +4492,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822469</v>
+        <v>119822434</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4527,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474129</v>
+        <v>474317</v>
       </c>
       <c r="R38" t="n">
-        <v>7074044</v>
+        <v>7073906</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4567,7 +4572,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4594,7 +4599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822434</v>
+        <v>119822420</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4634,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474317</v>
+        <v>474364</v>
       </c>
       <c r="R39" t="n">
-        <v>7073906</v>
+        <v>7073718</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4674,7 +4679,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4701,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822470</v>
+        <v>119822440</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4741,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474150</v>
+        <v>474401</v>
       </c>
       <c r="R40" t="n">
-        <v>7073954</v>
+        <v>7074148</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4781,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4808,10 +4813,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822489</v>
+        <v>119822484</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4824,21 +4829,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4848,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474517</v>
+        <v>474078</v>
       </c>
       <c r="R41" t="n">
-        <v>7073863</v>
+        <v>7074201</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4910,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822430</v>
+        <v>119822495</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4926,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474405</v>
+        <v>474155</v>
       </c>
       <c r="R42" t="n">
-        <v>7073873</v>
+        <v>7074201</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,11 +4991,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5017,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822438</v>
+        <v>119822455</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474363</v>
+        <v>474172</v>
       </c>
       <c r="R43" t="n">
-        <v>7074130</v>
+        <v>7074172</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,10 +5124,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822461</v>
+        <v>119822418</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5140,21 +5140,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474078</v>
+        <v>474133</v>
       </c>
       <c r="R44" t="n">
-        <v>7074226</v>
+        <v>7074227</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5200,11 +5200,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5231,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822428</v>
+        <v>119822490</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5242,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5271,10 +5266,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474418</v>
+        <v>474005</v>
       </c>
       <c r="R45" t="n">
-        <v>7073882</v>
+        <v>7073873</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5307,11 +5302,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5338,7 +5328,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822432</v>
+        <v>119822460</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5378,10 +5368,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474397</v>
+        <v>474092</v>
       </c>
       <c r="R46" t="n">
-        <v>7073871</v>
+        <v>7074245</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5418,7 +5408,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5445,7 +5435,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822456</v>
+        <v>119822445</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5485,10 +5475,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474160</v>
+        <v>474457</v>
       </c>
       <c r="R47" t="n">
-        <v>7074200</v>
+        <v>7074300</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5552,7 +5542,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119822437</v>
+        <v>119822424</v>
       </c>
       <c r="B48" t="n">
         <v>57310</v>
@@ -5592,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474345</v>
+        <v>474579</v>
       </c>
       <c r="R48" t="n">
-        <v>7074133</v>
+        <v>7073758</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5632,7 +5622,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,7 +5649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119822457</v>
+        <v>119822454</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5699,10 +5689,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474128</v>
+        <v>474182</v>
       </c>
       <c r="R49" t="n">
-        <v>7074233</v>
+        <v>7074153</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5739,7 +5729,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,7 +5756,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119822440</v>
+        <v>119822459</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -5806,10 +5796,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474401</v>
+        <v>474109</v>
       </c>
       <c r="R50" t="n">
-        <v>7074148</v>
+        <v>7074246</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5873,10 +5863,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119822491</v>
+        <v>119822458</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5889,21 +5879,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5913,10 +5903,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474386</v>
+        <v>474119</v>
       </c>
       <c r="R51" t="n">
-        <v>7074137</v>
+        <v>7074246</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5949,6 +5939,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,7 +5970,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119822431</v>
+        <v>119822441</v>
       </c>
       <c r="B52" t="n">
         <v>57310</v>
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474400</v>
+        <v>474422</v>
       </c>
       <c r="R52" t="n">
-        <v>7073871</v>
+        <v>7074145</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6055,7 +6050,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6082,10 +6077,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119822464</v>
+        <v>119822488</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6098,21 +6093,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6122,10 +6117,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474094</v>
+        <v>474121</v>
       </c>
       <c r="R53" t="n">
-        <v>7074062</v>
+        <v>7073951</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6158,11 +6153,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6189,7 +6179,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119822444</v>
+        <v>119822466</v>
       </c>
       <c r="B54" t="n">
         <v>57310</v>
@@ -6229,10 +6219,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474438</v>
+        <v>474121</v>
       </c>
       <c r="R54" t="n">
-        <v>7074241</v>
+        <v>7074052</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6296,10 +6286,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119822493</v>
+        <v>119822427</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6312,21 +6302,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6336,10 +6326,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474372</v>
+        <v>474530</v>
       </c>
       <c r="R55" t="n">
-        <v>7074297</v>
+        <v>7073855</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6372,6 +6362,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6398,10 +6393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119822486</v>
+        <v>119822444</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6414,21 +6409,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6438,10 +6433,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474121</v>
+        <v>474438</v>
       </c>
       <c r="R56" t="n">
-        <v>7074098</v>
+        <v>7074241</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6474,6 +6469,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6500,7 +6500,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119822455</v>
+        <v>119822470</v>
       </c>
       <c r="B57" t="n">
         <v>57310</v>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474172</v>
+        <v>474150</v>
       </c>
       <c r="R57" t="n">
-        <v>7074172</v>
+        <v>7073954</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6607,10 +6607,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119822481</v>
+        <v>119822474</v>
       </c>
       <c r="B58" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6623,21 +6623,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6647,10 +6647,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474105</v>
+        <v>474222</v>
       </c>
       <c r="R58" t="n">
-        <v>7074062</v>
+        <v>7073874</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6683,6 +6683,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6709,10 +6714,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119822439</v>
+        <v>119822489</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6725,21 +6730,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6749,10 +6754,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474378</v>
+        <v>474517</v>
       </c>
       <c r="R59" t="n">
-        <v>7074132</v>
+        <v>7073863</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6785,11 +6790,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6816,10 +6816,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119822418</v>
+        <v>119822485</v>
       </c>
       <c r="B60" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474133</v>
+        <v>474136</v>
       </c>
       <c r="R60" t="n">
-        <v>7074227</v>
+        <v>7074108</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6918,7 +6918,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119822460</v>
+        <v>119822443</v>
       </c>
       <c r="B61" t="n">
         <v>57310</v>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474092</v>
+        <v>474450</v>
       </c>
       <c r="R61" t="n">
-        <v>7074245</v>
+        <v>7074166</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7025,10 +7025,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119822484</v>
+        <v>119822469</v>
       </c>
       <c r="B62" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7041,21 +7041,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474078</v>
+        <v>474129</v>
       </c>
       <c r="R62" t="n">
-        <v>7074201</v>
+        <v>7074044</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7101,6 +7101,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7127,7 +7132,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119822429</v>
+        <v>119822476</v>
       </c>
       <c r="B63" t="n">
         <v>57310</v>
@@ -7167,10 +7172,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474415</v>
+        <v>474209</v>
       </c>
       <c r="R63" t="n">
-        <v>7073880</v>
+        <v>7073871</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7234,7 +7239,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119822442</v>
+        <v>119822433</v>
       </c>
       <c r="B64" t="n">
         <v>57310</v>
@@ -7274,10 +7279,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474435</v>
+        <v>474364</v>
       </c>
       <c r="R64" t="n">
-        <v>7074155</v>
+        <v>7073875</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7341,7 +7346,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119822467</v>
+        <v>119822475</v>
       </c>
       <c r="B65" t="n">
         <v>57310</v>
@@ -7381,10 +7386,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474148</v>
+        <v>474205</v>
       </c>
       <c r="R65" t="n">
-        <v>7074059</v>
+        <v>7073877</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7448,10 +7453,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119822433</v>
+        <v>119822417</v>
       </c>
       <c r="B66" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7464,21 +7469,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7488,10 +7493,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474364</v>
+        <v>474169</v>
       </c>
       <c r="R66" t="n">
-        <v>7073875</v>
+        <v>7074185</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7524,11 +7529,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119822495</v>
+        <v>119822429</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7571,21 +7571,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474155</v>
+        <v>474415</v>
       </c>
       <c r="R67" t="n">
-        <v>7074201</v>
+        <v>7073880</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7631,6 +7631,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7657,7 +7662,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822446</v>
+        <v>119822477</v>
       </c>
       <c r="B68" t="n">
         <v>57310</v>
@@ -7697,10 +7702,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474395</v>
+        <v>474098</v>
       </c>
       <c r="R68" t="n">
-        <v>7074319</v>
+        <v>7073885</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7764,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822443</v>
+        <v>119822486</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7780,21 +7785,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7804,10 +7809,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474450</v>
+        <v>474121</v>
       </c>
       <c r="R69" t="n">
-        <v>7074166</v>
+        <v>7074098</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7840,11 +7845,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7871,7 +7871,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119822450</v>
+        <v>119822448</v>
       </c>
       <c r="B70" t="n">
         <v>57310</v>
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474273</v>
+        <v>474334</v>
       </c>
       <c r="R70" t="n">
-        <v>7074232</v>
+        <v>7074241</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119822445</v>
+        <v>119822447</v>
       </c>
       <c r="B71" t="n">
         <v>57310</v>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474457</v>
+        <v>474350</v>
       </c>
       <c r="R71" t="n">
-        <v>7074300</v>
+        <v>7074246</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822452</v>
+        <v>119822450</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474233</v>
+        <v>474273</v>
       </c>
       <c r="R27" t="n">
-        <v>7074159</v>
+        <v>7074232</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822450</v>
+        <v>119822436</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474273</v>
+        <v>474298</v>
       </c>
       <c r="R28" t="n">
-        <v>7074232</v>
+        <v>7074026</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822436</v>
+        <v>119822452</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474298</v>
+        <v>474233</v>
       </c>
       <c r="R29" t="n">
-        <v>7074026</v>
+        <v>7074159</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -7346,10 +7346,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119822475</v>
+        <v>119822417</v>
       </c>
       <c r="B65" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7386,10 +7386,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474205</v>
+        <v>474169</v>
       </c>
       <c r="R65" t="n">
-        <v>7073877</v>
+        <v>7074185</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7422,11 +7422,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7453,10 +7448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119822417</v>
+        <v>119822475</v>
       </c>
       <c r="B66" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7469,21 +7464,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7493,10 +7488,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474169</v>
+        <v>474205</v>
       </c>
       <c r="R66" t="n">
-        <v>7074185</v>
+        <v>7073877</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7529,6 +7524,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119822429</v>
+        <v>119822486</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7571,21 +7571,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474415</v>
+        <v>474121</v>
       </c>
       <c r="R67" t="n">
-        <v>7073880</v>
+        <v>7074098</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7631,11 +7631,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7662,7 +7657,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822477</v>
+        <v>119822429</v>
       </c>
       <c r="B68" t="n">
         <v>57310</v>
@@ -7702,10 +7697,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474098</v>
+        <v>474415</v>
       </c>
       <c r="R68" t="n">
-        <v>7073885</v>
+        <v>7073880</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7769,10 +7764,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822486</v>
+        <v>119822477</v>
       </c>
       <c r="B69" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7785,21 +7780,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7809,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474121</v>
+        <v>474098</v>
       </c>
       <c r="R69" t="n">
-        <v>7074098</v>
+        <v>7073885</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7845,6 +7840,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822482</v>
+        <v>119822428</v>
       </c>
       <c r="B13" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474095</v>
+        <v>474418</v>
       </c>
       <c r="R13" t="n">
-        <v>7073945</v>
+        <v>7073882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822480</v>
+        <v>119822425</v>
       </c>
       <c r="B14" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474098</v>
+        <v>474571</v>
       </c>
       <c r="R14" t="n">
-        <v>7074059</v>
+        <v>7073868</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2015,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822428</v>
+        <v>119822471</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2076,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474418</v>
+        <v>474127</v>
       </c>
       <c r="R15" t="n">
-        <v>7073882</v>
+        <v>7073959</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822425</v>
+        <v>119822482</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474571</v>
+        <v>474095</v>
       </c>
       <c r="R16" t="n">
-        <v>7073868</v>
+        <v>7073945</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,11 +2229,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822471</v>
+        <v>119822480</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474127</v>
+        <v>474098</v>
       </c>
       <c r="R17" t="n">
-        <v>7073959</v>
+        <v>7074059</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822450</v>
+        <v>119822452</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474273</v>
+        <v>474233</v>
       </c>
       <c r="R27" t="n">
-        <v>7074232</v>
+        <v>7074159</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822436</v>
+        <v>119822450</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474298</v>
+        <v>474273</v>
       </c>
       <c r="R28" t="n">
-        <v>7074026</v>
+        <v>7074232</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822452</v>
+        <v>119822436</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474233</v>
+        <v>474298</v>
       </c>
       <c r="R29" t="n">
-        <v>7074159</v>
+        <v>7074026</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822491</v>
+        <v>119822451</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474386</v>
+        <v>474244</v>
       </c>
       <c r="R31" t="n">
-        <v>7074137</v>
+        <v>7074159</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,6 +3824,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3850,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822451</v>
+        <v>119822462</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3890,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474244</v>
+        <v>474099</v>
       </c>
       <c r="R32" t="n">
-        <v>7074159</v>
+        <v>7074178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3930,7 +3935,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,7 +3962,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822462</v>
+        <v>119822464</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -3997,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474099</v>
+        <v>474094</v>
       </c>
       <c r="R33" t="n">
-        <v>7074178</v>
+        <v>7074062</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4037,7 +4042,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822464</v>
+        <v>119822491</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474094</v>
+        <v>474386</v>
       </c>
       <c r="R34" t="n">
-        <v>7074062</v>
+        <v>7074137</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,11 +4145,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119822486</v>
+        <v>119822429</v>
       </c>
       <c r="B67" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7571,21 +7571,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474121</v>
+        <v>474415</v>
       </c>
       <c r="R67" t="n">
-        <v>7074098</v>
+        <v>7073880</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7631,6 +7631,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7657,7 +7662,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822429</v>
+        <v>119822477</v>
       </c>
       <c r="B68" t="n">
         <v>57310</v>
@@ -7697,10 +7702,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474415</v>
+        <v>474098</v>
       </c>
       <c r="R68" t="n">
-        <v>7073880</v>
+        <v>7073885</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7764,10 +7769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822477</v>
+        <v>119822486</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7780,21 +7785,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7804,10 +7809,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474098</v>
+        <v>474121</v>
       </c>
       <c r="R69" t="n">
-        <v>7073885</v>
+        <v>7074098</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7840,11 +7845,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822452</v>
+        <v>119822450</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474233</v>
+        <v>474273</v>
       </c>
       <c r="R27" t="n">
-        <v>7074159</v>
+        <v>7074232</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822450</v>
+        <v>119822436</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474273</v>
+        <v>474298</v>
       </c>
       <c r="R28" t="n">
-        <v>7074232</v>
+        <v>7074026</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822436</v>
+        <v>119822452</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474298</v>
+        <v>474233</v>
       </c>
       <c r="R29" t="n">
-        <v>7074026</v>
+        <v>7074159</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822451</v>
+        <v>119822491</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474244</v>
+        <v>474386</v>
       </c>
       <c r="R31" t="n">
-        <v>7074159</v>
+        <v>7074137</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,11 +3824,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822462</v>
+        <v>119822451</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3895,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474099</v>
+        <v>474244</v>
       </c>
       <c r="R32" t="n">
-        <v>7074178</v>
+        <v>7074159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,7 +3930,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822464</v>
+        <v>119822462</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4002,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474094</v>
+        <v>474099</v>
       </c>
       <c r="R33" t="n">
-        <v>7074062</v>
+        <v>7074178</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4037,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822491</v>
+        <v>119822464</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474386</v>
+        <v>474094</v>
       </c>
       <c r="R34" t="n">
-        <v>7074137</v>
+        <v>7074062</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,6 +4140,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822468</v>
+        <v>119822484</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474149</v>
+        <v>474078</v>
       </c>
       <c r="R35" t="n">
-        <v>7074055</v>
+        <v>7074201</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,11 +4247,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,10 +4273,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822422</v>
+        <v>119822495</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4294,21 +4289,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,10 +4313,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474382</v>
+        <v>474155</v>
       </c>
       <c r="R36" t="n">
-        <v>7073703</v>
+        <v>7074201</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4354,11 +4349,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,7 +4375,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822449</v>
+        <v>119822468</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4425,10 +4415,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474340</v>
+        <v>474149</v>
       </c>
       <c r="R37" t="n">
-        <v>7074246</v>
+        <v>7074055</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,7 +4482,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822434</v>
+        <v>119822422</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4532,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474317</v>
+        <v>474382</v>
       </c>
       <c r="R38" t="n">
-        <v>7073906</v>
+        <v>7073703</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4572,7 +4562,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,7 +4589,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822420</v>
+        <v>119822449</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4639,10 +4629,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474364</v>
+        <v>474340</v>
       </c>
       <c r="R39" t="n">
-        <v>7073718</v>
+        <v>7074246</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4679,7 +4669,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,7 +4696,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822440</v>
+        <v>119822434</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4746,10 +4736,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474401</v>
+        <v>474317</v>
       </c>
       <c r="R40" t="n">
-        <v>7074148</v>
+        <v>7073906</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4813,10 +4803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822484</v>
+        <v>119822420</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,21 +4819,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474078</v>
+        <v>474364</v>
       </c>
       <c r="R41" t="n">
-        <v>7074201</v>
+        <v>7073718</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4889,6 +4879,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4915,10 +4910,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822495</v>
+        <v>119822440</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4931,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4955,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474155</v>
+        <v>474401</v>
       </c>
       <c r="R42" t="n">
-        <v>7074201</v>
+        <v>7074148</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4991,6 +4986,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822439</v>
+        <v>119822467</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474378</v>
+        <v>474148</v>
       </c>
       <c r="R7" t="n">
-        <v>7074132</v>
+        <v>7074059</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822478</v>
+        <v>119822453</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474080</v>
+        <v>474191</v>
       </c>
       <c r="R8" t="n">
-        <v>7073873</v>
+        <v>7074152</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822467</v>
+        <v>119822439</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474148</v>
+        <v>474378</v>
       </c>
       <c r="R11" t="n">
-        <v>7074059</v>
+        <v>7074132</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822453</v>
+        <v>119822478</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474191</v>
+        <v>474080</v>
       </c>
       <c r="R12" t="n">
-        <v>7074152</v>
+        <v>7073873</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822450</v>
+        <v>119822452</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474273</v>
+        <v>474233</v>
       </c>
       <c r="R27" t="n">
-        <v>7074232</v>
+        <v>7074159</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822436</v>
+        <v>119822450</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474298</v>
+        <v>474273</v>
       </c>
       <c r="R28" t="n">
-        <v>7074026</v>
+        <v>7074232</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822452</v>
+        <v>119822436</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474233</v>
+        <v>474298</v>
       </c>
       <c r="R29" t="n">
-        <v>7074159</v>
+        <v>7074026</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4171,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822484</v>
+        <v>119822468</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474078</v>
+        <v>474149</v>
       </c>
       <c r="R35" t="n">
-        <v>7074201</v>
+        <v>7074055</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,6 +4247,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,10 +4278,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822495</v>
+        <v>119822422</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4289,21 +4294,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4313,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474155</v>
+        <v>474382</v>
       </c>
       <c r="R36" t="n">
-        <v>7074201</v>
+        <v>7073703</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4349,6 +4354,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822468</v>
+        <v>119822449</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4415,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474149</v>
+        <v>474340</v>
       </c>
       <c r="R37" t="n">
-        <v>7074055</v>
+        <v>7074246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,7 +4492,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822422</v>
+        <v>119822434</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4522,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474382</v>
+        <v>474317</v>
       </c>
       <c r="R38" t="n">
-        <v>7073703</v>
+        <v>7073906</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4562,7 +4572,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4589,7 +4599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822449</v>
+        <v>119822420</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4629,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474340</v>
+        <v>474364</v>
       </c>
       <c r="R39" t="n">
-        <v>7074246</v>
+        <v>7073718</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,7 +4679,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4696,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822434</v>
+        <v>119822440</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4736,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474317</v>
+        <v>474401</v>
       </c>
       <c r="R40" t="n">
-        <v>7073906</v>
+        <v>7074148</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,10 +4813,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822420</v>
+        <v>119822484</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4819,21 +4829,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4843,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474364</v>
+        <v>474078</v>
       </c>
       <c r="R41" t="n">
-        <v>7073718</v>
+        <v>7074201</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4879,11 +4889,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4910,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822440</v>
+        <v>119822495</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4926,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474401</v>
+        <v>474155</v>
       </c>
       <c r="R42" t="n">
-        <v>7074148</v>
+        <v>7074201</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,11 +4991,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119822429</v>
+        <v>119822486</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7571,21 +7571,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474415</v>
+        <v>474121</v>
       </c>
       <c r="R67" t="n">
-        <v>7073880</v>
+        <v>7074098</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7631,11 +7631,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7662,7 +7657,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822477</v>
+        <v>119822429</v>
       </c>
       <c r="B68" t="n">
         <v>57310</v>
@@ -7702,10 +7697,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474098</v>
+        <v>474415</v>
       </c>
       <c r="R68" t="n">
-        <v>7073885</v>
+        <v>7073880</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7769,10 +7764,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822486</v>
+        <v>119822477</v>
       </c>
       <c r="B69" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7785,21 +7780,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7809,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474121</v>
+        <v>474098</v>
       </c>
       <c r="R69" t="n">
-        <v>7074098</v>
+        <v>7073885</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7845,6 +7840,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822492</v>
+        <v>119822481</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474448</v>
+        <v>474105</v>
       </c>
       <c r="R2" t="n">
-        <v>7074194</v>
+        <v>7074062</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822419</v>
+        <v>119822492</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474170</v>
+        <v>474448</v>
       </c>
       <c r="R3" t="n">
-        <v>7073676</v>
+        <v>7074194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822442</v>
+        <v>119822461</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474435</v>
+        <v>474078</v>
       </c>
       <c r="R4" t="n">
-        <v>7074155</v>
+        <v>7074226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822481</v>
+        <v>119822419</v>
       </c>
       <c r="B5" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474105</v>
+        <v>474170</v>
       </c>
       <c r="R5" t="n">
-        <v>7074062</v>
+        <v>7073676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822461</v>
+        <v>119822442</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474078</v>
+        <v>474435</v>
       </c>
       <c r="R6" t="n">
-        <v>7074226</v>
+        <v>7074155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822452</v>
+        <v>119822450</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474233</v>
+        <v>474273</v>
       </c>
       <c r="R27" t="n">
-        <v>7074159</v>
+        <v>7074232</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822450</v>
+        <v>119822436</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474273</v>
+        <v>474298</v>
       </c>
       <c r="R28" t="n">
-        <v>7074232</v>
+        <v>7074026</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822436</v>
+        <v>119822452</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474298</v>
+        <v>474233</v>
       </c>
       <c r="R29" t="n">
-        <v>7074026</v>
+        <v>7074159</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822491</v>
+        <v>119822451</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474386</v>
+        <v>474244</v>
       </c>
       <c r="R31" t="n">
-        <v>7074137</v>
+        <v>7074159</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,6 +3824,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3850,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822451</v>
+        <v>119822462</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3890,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474244</v>
+        <v>474099</v>
       </c>
       <c r="R32" t="n">
-        <v>7074159</v>
+        <v>7074178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3930,7 +3935,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,7 +3962,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822462</v>
+        <v>119822464</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -3997,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474099</v>
+        <v>474094</v>
       </c>
       <c r="R33" t="n">
-        <v>7074178</v>
+        <v>7074062</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4037,7 +4042,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822464</v>
+        <v>119822491</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474094</v>
+        <v>474386</v>
       </c>
       <c r="R34" t="n">
-        <v>7074062</v>
+        <v>7074137</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,11 +4145,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822467</v>
+        <v>119822439</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474148</v>
+        <v>474378</v>
       </c>
       <c r="R7" t="n">
-        <v>7074059</v>
+        <v>7074132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822453</v>
+        <v>119822478</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474191</v>
+        <v>474080</v>
       </c>
       <c r="R8" t="n">
-        <v>7074152</v>
+        <v>7073873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822439</v>
+        <v>119822467</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474378</v>
+        <v>474148</v>
       </c>
       <c r="R11" t="n">
-        <v>7074132</v>
+        <v>7074059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822478</v>
+        <v>119822453</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474080</v>
+        <v>474191</v>
       </c>
       <c r="R12" t="n">
-        <v>7073873</v>
+        <v>7074152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822450</v>
+        <v>119822452</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474273</v>
+        <v>474233</v>
       </c>
       <c r="R27" t="n">
-        <v>7074232</v>
+        <v>7074159</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822436</v>
+        <v>119822450</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474298</v>
+        <v>474273</v>
       </c>
       <c r="R28" t="n">
-        <v>7074026</v>
+        <v>7074232</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822452</v>
+        <v>119822436</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474233</v>
+        <v>474298</v>
       </c>
       <c r="R29" t="n">
-        <v>7074159</v>
+        <v>7074026</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822481</v>
+        <v>119822471</v>
       </c>
       <c r="B2" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474105</v>
+        <v>474127</v>
       </c>
       <c r="R2" t="n">
-        <v>7074062</v>
+        <v>7073959</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822492</v>
+        <v>119822446</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474448</v>
+        <v>474395</v>
       </c>
       <c r="R3" t="n">
-        <v>7074194</v>
+        <v>7074319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822461</v>
+        <v>119822427</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474078</v>
+        <v>474530</v>
       </c>
       <c r="R4" t="n">
-        <v>7074226</v>
+        <v>7073855</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822419</v>
+        <v>119822424</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474170</v>
+        <v>474579</v>
       </c>
       <c r="R5" t="n">
-        <v>7073676</v>
+        <v>7073758</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822442</v>
+        <v>119822493</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474435</v>
+        <v>474372</v>
       </c>
       <c r="R6" t="n">
-        <v>7074155</v>
+        <v>7074297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822439</v>
+        <v>119822460</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474378</v>
+        <v>474092</v>
       </c>
       <c r="R7" t="n">
-        <v>7074132</v>
+        <v>7074245</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822478</v>
+        <v>119822453</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474080</v>
+        <v>474191</v>
       </c>
       <c r="R8" t="n">
-        <v>7073873</v>
+        <v>7074152</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822493</v>
+        <v>119822444</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474372</v>
+        <v>474438</v>
       </c>
       <c r="R9" t="n">
-        <v>7074297</v>
+        <v>7074241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822494</v>
+        <v>119822438</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474330</v>
+        <v>474363</v>
       </c>
       <c r="R10" t="n">
-        <v>7074260</v>
+        <v>7074130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822467</v>
+        <v>119822430</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474148</v>
+        <v>474405</v>
       </c>
       <c r="R11" t="n">
-        <v>7074059</v>
+        <v>7073873</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822453</v>
+        <v>119822484</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474191</v>
+        <v>474078</v>
       </c>
       <c r="R12" t="n">
-        <v>7074152</v>
+        <v>7074201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822428</v>
+        <v>119822422</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474418</v>
+        <v>474382</v>
       </c>
       <c r="R13" t="n">
-        <v>7073882</v>
+        <v>7073703</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822425</v>
+        <v>119822480</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474571</v>
+        <v>474098</v>
       </c>
       <c r="R14" t="n">
-        <v>7073868</v>
+        <v>7074059</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822471</v>
+        <v>119822445</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474127</v>
+        <v>474457</v>
       </c>
       <c r="R15" t="n">
-        <v>7073959</v>
+        <v>7074300</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822482</v>
+        <v>119822462</v>
       </c>
       <c r="B16" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474095</v>
+        <v>474099</v>
       </c>
       <c r="R16" t="n">
-        <v>7073945</v>
+        <v>7074178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822480</v>
+        <v>119822452</v>
       </c>
       <c r="B17" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474098</v>
+        <v>474233</v>
       </c>
       <c r="R17" t="n">
-        <v>7074059</v>
+        <v>7074159</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2341,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822430</v>
+        <v>119822434</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474405</v>
+        <v>474317</v>
       </c>
       <c r="R18" t="n">
-        <v>7073873</v>
+        <v>7073906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822438</v>
+        <v>119822423</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474363</v>
+        <v>474482</v>
       </c>
       <c r="R19" t="n">
-        <v>7074130</v>
+        <v>7073717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822456</v>
+        <v>119822440</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474160</v>
+        <v>474401</v>
       </c>
       <c r="R20" t="n">
-        <v>7074200</v>
+        <v>7074148</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822463</v>
+        <v>119822448</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474097</v>
+        <v>474334</v>
       </c>
       <c r="R21" t="n">
-        <v>7074133</v>
+        <v>7074241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822423</v>
+        <v>119822420</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474482</v>
+        <v>474364</v>
       </c>
       <c r="R22" t="n">
-        <v>7073717</v>
+        <v>7073718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822431</v>
+        <v>119822475</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2932,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474400</v>
+        <v>474205</v>
       </c>
       <c r="R23" t="n">
-        <v>7073871</v>
+        <v>7073877</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822437</v>
+        <v>119822495</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474345</v>
+        <v>474155</v>
       </c>
       <c r="R24" t="n">
-        <v>7074133</v>
+        <v>7074201</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,11 +3090,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822457</v>
+        <v>119822428</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3146,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474128</v>
+        <v>474418</v>
       </c>
       <c r="R25" t="n">
-        <v>7074233</v>
+        <v>7073882</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822446</v>
+        <v>119822467</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3253,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474395</v>
+        <v>474148</v>
       </c>
       <c r="R26" t="n">
-        <v>7074319</v>
+        <v>7074059</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822452</v>
+        <v>119822474</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474233</v>
+        <v>474222</v>
       </c>
       <c r="R27" t="n">
-        <v>7074159</v>
+        <v>7073874</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822450</v>
+        <v>119822470</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474273</v>
+        <v>474150</v>
       </c>
       <c r="R28" t="n">
-        <v>7074232</v>
+        <v>7073954</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822436</v>
+        <v>119822457</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3574,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474298</v>
+        <v>474128</v>
       </c>
       <c r="R29" t="n">
-        <v>7074026</v>
+        <v>7074233</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3624,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822432</v>
+        <v>119822463</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474397</v>
+        <v>474097</v>
       </c>
       <c r="R30" t="n">
-        <v>7073871</v>
+        <v>7074133</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822451</v>
+        <v>119822478</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474244</v>
+        <v>474080</v>
       </c>
       <c r="R31" t="n">
-        <v>7074159</v>
+        <v>7073873</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822462</v>
+        <v>119822458</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3895,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474099</v>
+        <v>474119</v>
       </c>
       <c r="R32" t="n">
-        <v>7074178</v>
+        <v>7074246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,7 +3945,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822464</v>
+        <v>119822429</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4002,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474094</v>
+        <v>474415</v>
       </c>
       <c r="R33" t="n">
-        <v>7074062</v>
+        <v>7073880</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4052,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822491</v>
+        <v>119822477</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4095,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474386</v>
+        <v>474098</v>
       </c>
       <c r="R34" t="n">
-        <v>7074137</v>
+        <v>7073885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,6 +4155,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,10 +4186,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822468</v>
+        <v>119822456</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4211,10 +4226,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474149</v>
+        <v>474160</v>
       </c>
       <c r="R35" t="n">
-        <v>7074055</v>
+        <v>7074200</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4278,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822422</v>
+        <v>119822433</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4318,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474382</v>
+        <v>474364</v>
       </c>
       <c r="R36" t="n">
-        <v>7073703</v>
+        <v>7073875</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,7 +4373,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,10 +4400,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822449</v>
+        <v>119822425</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4425,10 +4440,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474340</v>
+        <v>474571</v>
       </c>
       <c r="R37" t="n">
-        <v>7074246</v>
+        <v>7073868</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,10 +4507,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822434</v>
+        <v>119822494</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4508,21 +4523,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4532,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474317</v>
+        <v>474330</v>
       </c>
       <c r="R38" t="n">
-        <v>7073906</v>
+        <v>7074260</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4568,11 +4583,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,10 +4609,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822420</v>
+        <v>119822469</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4639,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474364</v>
+        <v>474129</v>
       </c>
       <c r="R39" t="n">
-        <v>7073718</v>
+        <v>7074044</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4679,7 +4689,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822440</v>
+        <v>119822490</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4722,21 +4732,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4756,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474401</v>
+        <v>474005</v>
       </c>
       <c r="R40" t="n">
-        <v>7074148</v>
+        <v>7073873</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,11 +4792,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4813,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822484</v>
+        <v>119822431</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474078</v>
+        <v>474400</v>
       </c>
       <c r="R41" t="n">
-        <v>7074201</v>
+        <v>7073871</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4889,6 +4894,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4915,10 +4925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822495</v>
+        <v>119822459</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4931,21 +4941,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4955,10 +4965,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474155</v>
+        <v>474109</v>
       </c>
       <c r="R42" t="n">
-        <v>7074201</v>
+        <v>7074246</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4991,6 +5001,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,10 +5032,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822455</v>
+        <v>119822489</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5033,21 +5048,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5057,10 +5072,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474172</v>
+        <v>474517</v>
       </c>
       <c r="R43" t="n">
-        <v>7074172</v>
+        <v>7073863</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5093,11 +5108,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5124,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822418</v>
+        <v>119822449</v>
       </c>
       <c r="B44" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5140,21 +5150,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5164,10 +5174,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474133</v>
+        <v>474340</v>
       </c>
       <c r="R44" t="n">
-        <v>7074227</v>
+        <v>7074246</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5200,6 +5210,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5226,10 +5241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822490</v>
+        <v>119822476</v>
       </c>
       <c r="B45" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5242,21 +5257,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5266,10 +5281,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474005</v>
+        <v>474209</v>
       </c>
       <c r="R45" t="n">
-        <v>7073873</v>
+        <v>7073871</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5302,6 +5317,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5328,10 +5348,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822460</v>
+        <v>119822432</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5368,10 +5388,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474092</v>
+        <v>474397</v>
       </c>
       <c r="R46" t="n">
-        <v>7074245</v>
+        <v>7073871</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5408,7 +5428,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5435,10 +5455,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822445</v>
+        <v>119822486</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5451,21 +5471,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5475,10 +5495,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474457</v>
+        <v>474121</v>
       </c>
       <c r="R47" t="n">
-        <v>7074300</v>
+        <v>7074098</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5511,11 +5531,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5542,10 +5557,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119822424</v>
+        <v>119822451</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5582,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474579</v>
+        <v>474244</v>
       </c>
       <c r="R48" t="n">
-        <v>7073758</v>
+        <v>7074159</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5622,7 +5637,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5649,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119822454</v>
+        <v>119822418</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5665,21 +5680,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5689,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474182</v>
+        <v>474133</v>
       </c>
       <c r="R49" t="n">
-        <v>7074153</v>
+        <v>7074227</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5725,11 +5740,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5756,10 +5766,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119822459</v>
+        <v>119822491</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5772,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5796,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474109</v>
+        <v>474386</v>
       </c>
       <c r="R50" t="n">
-        <v>7074246</v>
+        <v>7074137</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5832,11 +5842,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5863,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119822458</v>
+        <v>119822492</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5879,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5903,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474119</v>
+        <v>474448</v>
       </c>
       <c r="R51" t="n">
-        <v>7074246</v>
+        <v>7074194</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5939,11 +5944,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119822441</v>
+        <v>119822439</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474422</v>
+        <v>474378</v>
       </c>
       <c r="R52" t="n">
-        <v>7074145</v>
+        <v>7074132</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6077,10 +6077,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119822488</v>
+        <v>119822443</v>
       </c>
       <c r="B53" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6093,21 +6093,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6117,10 +6117,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474121</v>
+        <v>474450</v>
       </c>
       <c r="R53" t="n">
-        <v>7073951</v>
+        <v>7074166</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6153,6 +6153,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6179,10 +6184,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119822466</v>
+        <v>119822488</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6195,21 +6200,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6222,7 +6227,7 @@
         <v>474121</v>
       </c>
       <c r="R54" t="n">
-        <v>7074052</v>
+        <v>7073951</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6255,11 +6260,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6286,10 +6286,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119822427</v>
+        <v>119822466</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474530</v>
+        <v>474121</v>
       </c>
       <c r="R55" t="n">
-        <v>7073855</v>
+        <v>7074052</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6393,10 +6393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119822444</v>
+        <v>119822417</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6409,21 +6409,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474438</v>
+        <v>474169</v>
       </c>
       <c r="R56" t="n">
-        <v>7074241</v>
+        <v>7074185</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6469,11 +6469,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6500,10 +6495,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119822470</v>
+        <v>119822437</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6540,10 +6535,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474150</v>
+        <v>474345</v>
       </c>
       <c r="R57" t="n">
-        <v>7073954</v>
+        <v>7074133</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6580,7 +6575,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6607,10 +6602,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119822474</v>
+        <v>119822450</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6647,10 +6642,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474222</v>
+        <v>474273</v>
       </c>
       <c r="R58" t="n">
-        <v>7073874</v>
+        <v>7074232</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6687,7 +6682,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6714,10 +6709,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119822489</v>
+        <v>119822441</v>
       </c>
       <c r="B59" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6730,21 +6725,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6754,10 +6749,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474517</v>
+        <v>474422</v>
       </c>
       <c r="R59" t="n">
-        <v>7073863</v>
+        <v>7074145</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6790,6 +6785,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6819,7 +6819,7 @@
         <v>119822485</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119822443</v>
+        <v>119822455</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474450</v>
+        <v>474172</v>
       </c>
       <c r="R61" t="n">
-        <v>7074166</v>
+        <v>7074172</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7025,10 +7025,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119822469</v>
+        <v>119822436</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474129</v>
+        <v>474298</v>
       </c>
       <c r="R62" t="n">
-        <v>7074044</v>
+        <v>7074026</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7132,10 +7132,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119822476</v>
+        <v>119822419</v>
       </c>
       <c r="B63" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474209</v>
+        <v>474170</v>
       </c>
       <c r="R63" t="n">
-        <v>7073871</v>
+        <v>7073676</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119822433</v>
+        <v>119822442</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474364</v>
+        <v>474435</v>
       </c>
       <c r="R64" t="n">
-        <v>7073875</v>
+        <v>7074155</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7346,10 +7346,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119822417</v>
+        <v>119822447</v>
       </c>
       <c r="B65" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7386,10 +7386,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474169</v>
+        <v>474350</v>
       </c>
       <c r="R65" t="n">
-        <v>7074185</v>
+        <v>7074246</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7422,6 +7422,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7448,10 +7453,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119822475</v>
+        <v>119822481</v>
       </c>
       <c r="B66" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7464,21 +7469,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7488,10 +7493,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474205</v>
+        <v>474105</v>
       </c>
       <c r="R66" t="n">
-        <v>7073877</v>
+        <v>7074062</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7524,11 +7529,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119822486</v>
+        <v>119822468</v>
       </c>
       <c r="B67" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7571,21 +7571,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474121</v>
+        <v>474149</v>
       </c>
       <c r="R67" t="n">
-        <v>7074098</v>
+        <v>7074055</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7631,6 +7631,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7657,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822429</v>
+        <v>119822482</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7673,21 +7678,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7697,10 +7702,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474415</v>
+        <v>474095</v>
       </c>
       <c r="R68" t="n">
-        <v>7073880</v>
+        <v>7073945</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7733,11 +7738,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7764,10 +7764,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822477</v>
+        <v>119822454</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7804,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474098</v>
+        <v>474182</v>
       </c>
       <c r="R69" t="n">
-        <v>7073885</v>
+        <v>7074153</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7871,10 +7871,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119822448</v>
+        <v>119822461</v>
       </c>
       <c r="B70" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474334</v>
+        <v>474078</v>
       </c>
       <c r="R70" t="n">
-        <v>7074241</v>
+        <v>7074226</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7978,10 +7978,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119822447</v>
+        <v>119822464</v>
       </c>
       <c r="B71" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474350</v>
+        <v>474094</v>
       </c>
       <c r="R71" t="n">
-        <v>7074246</v>
+        <v>7074062</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822471</v>
+        <v>119822493</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474127</v>
+        <v>474372</v>
       </c>
       <c r="R2" t="n">
-        <v>7073959</v>
+        <v>7074297</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822493</v>
+        <v>119822471</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474372</v>
+        <v>474127</v>
       </c>
       <c r="R6" t="n">
-        <v>7074297</v>
+        <v>7073959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3972,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822429</v>
+        <v>119822494</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,21 +3988,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474415</v>
+        <v>474330</v>
       </c>
       <c r="R33" t="n">
-        <v>7073880</v>
+        <v>7074260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4048,11 +4048,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,7 +4074,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822477</v>
+        <v>119822469</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474098</v>
+        <v>474129</v>
       </c>
       <c r="R34" t="n">
-        <v>7073885</v>
+        <v>7074044</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4159,7 +4154,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4186,7 +4181,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822456</v>
+        <v>119822429</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4226,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474160</v>
+        <v>474415</v>
       </c>
       <c r="R35" t="n">
-        <v>7074200</v>
+        <v>7073880</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822433</v>
+        <v>119822490</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4309,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4333,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474364</v>
+        <v>474005</v>
       </c>
       <c r="R36" t="n">
-        <v>7073875</v>
+        <v>7073873</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4369,11 +4364,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4400,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822425</v>
+        <v>119822477</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4440,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474571</v>
+        <v>474098</v>
       </c>
       <c r="R37" t="n">
-        <v>7073868</v>
+        <v>7073885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4507,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822494</v>
+        <v>119822456</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4523,21 +4513,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4547,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474330</v>
+        <v>474160</v>
       </c>
       <c r="R38" t="n">
-        <v>7074260</v>
+        <v>7074200</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4583,6 +4573,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4609,7 +4604,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822469</v>
+        <v>119822433</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474129</v>
+        <v>474364</v>
       </c>
       <c r="R39" t="n">
-        <v>7074044</v>
+        <v>7073875</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4689,7 +4684,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822490</v>
+        <v>119822425</v>
       </c>
       <c r="B40" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4732,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4756,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474005</v>
+        <v>474571</v>
       </c>
       <c r="R40" t="n">
-        <v>7073873</v>
+        <v>7073868</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,6 +4787,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -7662,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822482</v>
+        <v>119822454</v>
       </c>
       <c r="B68" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7678,21 +7678,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474095</v>
+        <v>474182</v>
       </c>
       <c r="R68" t="n">
-        <v>7073945</v>
+        <v>7074153</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7738,6 +7738,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7764,7 +7769,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822454</v>
+        <v>119822461</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -7804,10 +7809,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474182</v>
+        <v>474078</v>
       </c>
       <c r="R69" t="n">
-        <v>7074153</v>
+        <v>7074226</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7844,7 +7849,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7871,10 +7876,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119822461</v>
+        <v>119822482</v>
       </c>
       <c r="B70" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7887,21 +7892,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7911,10 +7916,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474078</v>
+        <v>474095</v>
       </c>
       <c r="R70" t="n">
-        <v>7074226</v>
+        <v>7073945</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7947,11 +7952,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822493</v>
+        <v>119822420</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474372</v>
+        <v>474364</v>
       </c>
       <c r="R2" t="n">
-        <v>7074297</v>
+        <v>7073718</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822446</v>
+        <v>119822425</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474395</v>
+        <v>474571</v>
       </c>
       <c r="R3" t="n">
-        <v>7074319</v>
+        <v>7073868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822427</v>
+        <v>119822430</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474530</v>
+        <v>474405</v>
       </c>
       <c r="R4" t="n">
-        <v>7073855</v>
+        <v>7073873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822424</v>
+        <v>119822461</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474579</v>
+        <v>474078</v>
       </c>
       <c r="R5" t="n">
-        <v>7073758</v>
+        <v>7074226</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822471</v>
+        <v>119822417</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474127</v>
+        <v>474169</v>
       </c>
       <c r="R6" t="n">
-        <v>7073959</v>
+        <v>7074185</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822460</v>
+        <v>119822454</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474092</v>
+        <v>474182</v>
       </c>
       <c r="R7" t="n">
-        <v>7074245</v>
+        <v>7074153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822453</v>
+        <v>119822455</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474191</v>
+        <v>474172</v>
       </c>
       <c r="R8" t="n">
-        <v>7074152</v>
+        <v>7074172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822444</v>
+        <v>119822422</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474438</v>
+        <v>474382</v>
       </c>
       <c r="R9" t="n">
-        <v>7074241</v>
+        <v>7073703</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822438</v>
+        <v>119822437</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474363</v>
+        <v>474345</v>
       </c>
       <c r="R10" t="n">
-        <v>7074130</v>
+        <v>7074133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822430</v>
+        <v>119822471</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474405</v>
+        <v>474127</v>
       </c>
       <c r="R11" t="n">
-        <v>7073873</v>
+        <v>7073959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822484</v>
+        <v>119822482</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474078</v>
+        <v>474095</v>
       </c>
       <c r="R12" t="n">
-        <v>7074201</v>
+        <v>7073945</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822422</v>
+        <v>119822469</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474382</v>
+        <v>474129</v>
       </c>
       <c r="R13" t="n">
-        <v>7073703</v>
+        <v>7074044</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822480</v>
+        <v>119822424</v>
       </c>
       <c r="B14" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474098</v>
+        <v>474579</v>
       </c>
       <c r="R14" t="n">
-        <v>7074059</v>
+        <v>7073758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822445</v>
+        <v>119822475</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474457</v>
+        <v>474205</v>
       </c>
       <c r="R15" t="n">
-        <v>7074300</v>
+        <v>7073877</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822462</v>
+        <v>119822490</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474099</v>
+        <v>474005</v>
       </c>
       <c r="R16" t="n">
-        <v>7074178</v>
+        <v>7073873</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822452</v>
+        <v>119822463</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474233</v>
+        <v>474097</v>
       </c>
       <c r="R17" t="n">
-        <v>7074159</v>
+        <v>7074133</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822434</v>
+        <v>119822491</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474317</v>
+        <v>474386</v>
       </c>
       <c r="R18" t="n">
-        <v>7073906</v>
+        <v>7074137</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,11 +2448,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822423</v>
+        <v>119822489</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474482</v>
+        <v>474517</v>
       </c>
       <c r="R19" t="n">
-        <v>7073717</v>
+        <v>7073863</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,11 +2550,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822440</v>
+        <v>119822449</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2626,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474401</v>
+        <v>474340</v>
       </c>
       <c r="R20" t="n">
-        <v>7074148</v>
+        <v>7074246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822448</v>
+        <v>119822434</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2733,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474334</v>
+        <v>474317</v>
       </c>
       <c r="R21" t="n">
-        <v>7074241</v>
+        <v>7073906</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2763,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2790,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822420</v>
+        <v>119822423</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2840,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474364</v>
+        <v>474482</v>
       </c>
       <c r="R22" t="n">
-        <v>7073718</v>
+        <v>7073717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2870,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822475</v>
+        <v>119822451</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2947,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474205</v>
+        <v>474244</v>
       </c>
       <c r="R23" t="n">
-        <v>7073877</v>
+        <v>7074159</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822495</v>
+        <v>119822433</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3020,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474155</v>
+        <v>474364</v>
       </c>
       <c r="R24" t="n">
-        <v>7074201</v>
+        <v>7073875</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,6 +3080,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822428</v>
+        <v>119822418</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474418</v>
+        <v>474133</v>
       </c>
       <c r="R25" t="n">
-        <v>7073882</v>
+        <v>7074227</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,11 +3187,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822467</v>
+        <v>119822481</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474148</v>
+        <v>474105</v>
       </c>
       <c r="R26" t="n">
-        <v>7074059</v>
+        <v>7074062</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,11 +3289,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822474</v>
+        <v>119822494</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,21 +3331,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474222</v>
+        <v>474330</v>
       </c>
       <c r="R27" t="n">
-        <v>7073874</v>
+        <v>7074260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,11 +3391,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,7 +3417,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822470</v>
+        <v>119822468</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3477,10 +3457,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474150</v>
+        <v>474149</v>
       </c>
       <c r="R28" t="n">
-        <v>7073954</v>
+        <v>7074055</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,7 +3497,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,7 +3524,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822457</v>
+        <v>119822446</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3584,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474128</v>
+        <v>474395</v>
       </c>
       <c r="R29" t="n">
-        <v>7074233</v>
+        <v>7074319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,7 +3631,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822463</v>
+        <v>119822466</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3691,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474097</v>
+        <v>474121</v>
       </c>
       <c r="R30" t="n">
-        <v>7074133</v>
+        <v>7074052</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3711,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,7 +3738,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822478</v>
+        <v>119822453</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3798,10 +3778,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474080</v>
+        <v>474191</v>
       </c>
       <c r="R31" t="n">
-        <v>7073873</v>
+        <v>7074152</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3865,7 +3845,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822458</v>
+        <v>119822470</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3905,10 +3885,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474119</v>
+        <v>474150</v>
       </c>
       <c r="R32" t="n">
-        <v>7074246</v>
+        <v>7073954</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3925,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,10 +3952,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822494</v>
+        <v>119822485</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,21 +3968,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474330</v>
+        <v>474136</v>
       </c>
       <c r="R33" t="n">
-        <v>7074260</v>
+        <v>7074108</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,7 +4054,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822469</v>
+        <v>119822477</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4114,10 +4094,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474129</v>
+        <v>474098</v>
       </c>
       <c r="R34" t="n">
-        <v>7074044</v>
+        <v>7073885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,7 +4134,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822429</v>
+        <v>119822493</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,21 +4177,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,10 +4201,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474415</v>
+        <v>474372</v>
       </c>
       <c r="R35" t="n">
-        <v>7073880</v>
+        <v>7074297</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,11 +4237,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,10 +4263,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822490</v>
+        <v>119822431</v>
       </c>
       <c r="B36" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4304,21 +4279,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474005</v>
+        <v>474400</v>
       </c>
       <c r="R36" t="n">
-        <v>7073873</v>
+        <v>7073871</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4364,6 +4339,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4370,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822477</v>
+        <v>119822442</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4430,10 +4410,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474098</v>
+        <v>474435</v>
       </c>
       <c r="R37" t="n">
-        <v>7073885</v>
+        <v>7074155</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,7 +4477,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822456</v>
+        <v>119822458</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4537,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474160</v>
+        <v>474119</v>
       </c>
       <c r="R38" t="n">
-        <v>7074200</v>
+        <v>7074246</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4604,7 +4584,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822433</v>
+        <v>119822436</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4644,10 +4624,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474364</v>
+        <v>474298</v>
       </c>
       <c r="R39" t="n">
-        <v>7073875</v>
+        <v>7074026</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,7 +4664,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,7 +4691,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822425</v>
+        <v>119822428</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4751,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474571</v>
+        <v>474418</v>
       </c>
       <c r="R40" t="n">
-        <v>7073868</v>
+        <v>7073882</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4818,7 +4798,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822431</v>
+        <v>119822464</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4858,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474400</v>
+        <v>474094</v>
       </c>
       <c r="R41" t="n">
-        <v>7073871</v>
+        <v>7074062</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,7 +4878,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4925,7 +4905,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822459</v>
+        <v>119822447</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4965,7 +4945,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474109</v>
+        <v>474350</v>
       </c>
       <c r="R42" t="n">
         <v>7074246</v>
@@ -5032,10 +5012,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822489</v>
+        <v>119822440</v>
       </c>
       <c r="B43" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5048,21 +5028,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5072,10 +5052,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474517</v>
+        <v>474401</v>
       </c>
       <c r="R43" t="n">
-        <v>7073863</v>
+        <v>7074148</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5108,6 +5088,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5134,7 +5119,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822449</v>
+        <v>119822429</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5174,10 +5159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474340</v>
+        <v>474415</v>
       </c>
       <c r="R44" t="n">
-        <v>7074246</v>
+        <v>7073880</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5241,7 +5226,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822476</v>
+        <v>119822452</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5281,10 +5266,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474209</v>
+        <v>474233</v>
       </c>
       <c r="R45" t="n">
-        <v>7073871</v>
+        <v>7074159</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5348,7 +5333,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822432</v>
+        <v>119822427</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5388,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474397</v>
+        <v>474530</v>
       </c>
       <c r="R46" t="n">
-        <v>7073871</v>
+        <v>7073855</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5428,7 +5413,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5455,10 +5440,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822486</v>
+        <v>119822495</v>
       </c>
       <c r="B47" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5471,21 +5456,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5495,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474121</v>
+        <v>474155</v>
       </c>
       <c r="R47" t="n">
-        <v>7074098</v>
+        <v>7074201</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5557,10 +5542,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119822451</v>
+        <v>119822492</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5573,21 +5558,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5597,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474244</v>
+        <v>474448</v>
       </c>
       <c r="R48" t="n">
-        <v>7074159</v>
+        <v>7074194</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5633,11 +5618,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,10 +5644,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119822418</v>
+        <v>119822486</v>
       </c>
       <c r="B49" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5680,21 +5660,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5704,10 +5684,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474133</v>
+        <v>474121</v>
       </c>
       <c r="R49" t="n">
-        <v>7074227</v>
+        <v>7074098</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5766,10 +5746,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119822491</v>
+        <v>119822488</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5782,21 +5762,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5786,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474386</v>
+        <v>474121</v>
       </c>
       <c r="R50" t="n">
-        <v>7074137</v>
+        <v>7073951</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5868,10 +5848,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119822492</v>
+        <v>119822460</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5864,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5888,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474448</v>
+        <v>474092</v>
       </c>
       <c r="R51" t="n">
-        <v>7074194</v>
+        <v>7074245</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5944,6 +5924,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,7 +5955,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119822439</v>
+        <v>119822438</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -6010,10 +5995,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474378</v>
+        <v>474363</v>
       </c>
       <c r="R52" t="n">
-        <v>7074132</v>
+        <v>7074130</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6050,7 +6035,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6077,7 +6062,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119822443</v>
+        <v>119822448</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6117,10 +6102,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474450</v>
+        <v>474334</v>
       </c>
       <c r="R53" t="n">
-        <v>7074166</v>
+        <v>7074241</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6157,7 +6142,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6184,10 +6169,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119822488</v>
+        <v>119822456</v>
       </c>
       <c r="B54" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6200,21 +6185,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6224,10 +6209,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474121</v>
+        <v>474160</v>
       </c>
       <c r="R54" t="n">
-        <v>7073951</v>
+        <v>7074200</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6260,6 +6245,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6286,7 +6276,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119822466</v>
+        <v>119822419</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6326,10 +6316,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474121</v>
+        <v>474170</v>
       </c>
       <c r="R55" t="n">
-        <v>7074052</v>
+        <v>7073676</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6366,7 +6356,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6393,10 +6383,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119822417</v>
+        <v>119822462</v>
       </c>
       <c r="B56" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6409,21 +6399,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6433,10 +6423,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474169</v>
+        <v>474099</v>
       </c>
       <c r="R56" t="n">
-        <v>7074185</v>
+        <v>7074178</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6469,6 +6459,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6495,7 +6490,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119822437</v>
+        <v>119822439</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6535,10 +6530,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474345</v>
+        <v>474378</v>
       </c>
       <c r="R57" t="n">
-        <v>7074133</v>
+        <v>7074132</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6575,7 +6570,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6602,7 +6597,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119822450</v>
+        <v>119822467</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6642,10 +6637,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474273</v>
+        <v>474148</v>
       </c>
       <c r="R58" t="n">
-        <v>7074232</v>
+        <v>7074059</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6682,7 +6677,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6709,7 +6704,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119822441</v>
+        <v>119822457</v>
       </c>
       <c r="B59" t="n">
         <v>57320</v>
@@ -6749,10 +6744,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474422</v>
+        <v>474128</v>
       </c>
       <c r="R59" t="n">
-        <v>7074145</v>
+        <v>7074233</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6816,10 +6811,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119822485</v>
+        <v>119822474</v>
       </c>
       <c r="B60" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6832,21 +6827,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6856,10 +6851,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474136</v>
+        <v>474222</v>
       </c>
       <c r="R60" t="n">
-        <v>7074108</v>
+        <v>7073874</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6892,6 +6887,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6918,7 +6918,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119822455</v>
+        <v>119822478</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474172</v>
+        <v>474080</v>
       </c>
       <c r="R61" t="n">
-        <v>7074172</v>
+        <v>7073873</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7025,10 +7025,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119822436</v>
+        <v>119822484</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7041,21 +7041,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474298</v>
+        <v>474078</v>
       </c>
       <c r="R62" t="n">
-        <v>7074026</v>
+        <v>7074201</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7101,11 +7101,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7132,10 +7127,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119822419</v>
+        <v>119822480</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7148,21 +7143,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7172,10 +7167,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474170</v>
+        <v>474098</v>
       </c>
       <c r="R63" t="n">
-        <v>7073676</v>
+        <v>7074059</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,11 +7203,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7239,7 +7229,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119822442</v>
+        <v>119822445</v>
       </c>
       <c r="B64" t="n">
         <v>57320</v>
@@ -7279,10 +7269,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474435</v>
+        <v>474457</v>
       </c>
       <c r="R64" t="n">
-        <v>7074155</v>
+        <v>7074300</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7346,7 +7336,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119822447</v>
+        <v>119822441</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7386,10 +7376,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474350</v>
+        <v>474422</v>
       </c>
       <c r="R65" t="n">
-        <v>7074246</v>
+        <v>7074145</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7453,10 +7443,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119822481</v>
+        <v>119822476</v>
       </c>
       <c r="B66" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7469,21 +7459,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7493,10 +7483,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474105</v>
+        <v>474209</v>
       </c>
       <c r="R66" t="n">
-        <v>7074062</v>
+        <v>7073871</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7529,6 +7519,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,7 +7550,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119822468</v>
+        <v>119822443</v>
       </c>
       <c r="B67" t="n">
         <v>57320</v>
@@ -7595,10 +7590,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474149</v>
+        <v>474450</v>
       </c>
       <c r="R67" t="n">
-        <v>7074055</v>
+        <v>7074166</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7662,7 +7657,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822454</v>
+        <v>119822444</v>
       </c>
       <c r="B68" t="n">
         <v>57320</v>
@@ -7702,10 +7697,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474182</v>
+        <v>474438</v>
       </c>
       <c r="R68" t="n">
-        <v>7074153</v>
+        <v>7074241</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7769,7 +7764,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822461</v>
+        <v>119822450</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -7809,10 +7804,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474078</v>
+        <v>474273</v>
       </c>
       <c r="R69" t="n">
-        <v>7074226</v>
+        <v>7074232</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7849,7 +7844,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7876,10 +7871,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119822482</v>
+        <v>119822432</v>
       </c>
       <c r="B70" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7892,21 +7887,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7916,10 +7911,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474095</v>
+        <v>474397</v>
       </c>
       <c r="R70" t="n">
-        <v>7073945</v>
+        <v>7073871</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7952,6 +7947,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7978,7 +7978,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119822464</v>
+        <v>119822459</v>
       </c>
       <c r="B71" t="n">
         <v>57320</v>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474094</v>
+        <v>474109</v>
       </c>
       <c r="R71" t="n">
-        <v>7074062</v>
+        <v>7074246</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822417</v>
+        <v>119822482</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474169</v>
+        <v>474095</v>
       </c>
       <c r="R6" t="n">
-        <v>7074185</v>
+        <v>7073945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822454</v>
+        <v>119822417</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474182</v>
+        <v>474169</v>
       </c>
       <c r="R7" t="n">
-        <v>7074153</v>
+        <v>7074185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822455</v>
+        <v>119822454</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474172</v>
+        <v>474182</v>
       </c>
       <c r="R8" t="n">
-        <v>7074172</v>
+        <v>7074153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822422</v>
+        <v>119822455</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474382</v>
+        <v>474172</v>
       </c>
       <c r="R9" t="n">
-        <v>7073703</v>
+        <v>7074172</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822437</v>
+        <v>119822422</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474345</v>
+        <v>474382</v>
       </c>
       <c r="R10" t="n">
-        <v>7074133</v>
+        <v>7073703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822471</v>
+        <v>119822437</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474127</v>
+        <v>474345</v>
       </c>
       <c r="R11" t="n">
-        <v>7073959</v>
+        <v>7074133</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822482</v>
+        <v>119822471</v>
       </c>
       <c r="B12" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474095</v>
+        <v>474127</v>
       </c>
       <c r="R12" t="n">
-        <v>7073945</v>
+        <v>7073959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822489</v>
+        <v>119822449</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474517</v>
+        <v>474340</v>
       </c>
       <c r="R19" t="n">
-        <v>7073863</v>
+        <v>7074246</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,6 +2550,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822449</v>
+        <v>119822434</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2616,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474340</v>
+        <v>474317</v>
       </c>
       <c r="R20" t="n">
-        <v>7074246</v>
+        <v>7073906</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822434</v>
+        <v>119822423</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474317</v>
+        <v>474482</v>
       </c>
       <c r="R21" t="n">
-        <v>7073906</v>
+        <v>7073717</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2768,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822423</v>
+        <v>119822489</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474482</v>
+        <v>474517</v>
       </c>
       <c r="R22" t="n">
-        <v>7073717</v>
+        <v>7073863</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,11 +2871,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822451</v>
+        <v>119822418</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474244</v>
+        <v>474133</v>
       </c>
       <c r="R23" t="n">
-        <v>7074159</v>
+        <v>7074227</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,11 +2973,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,7 +2999,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822433</v>
+        <v>119822451</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474364</v>
+        <v>474244</v>
       </c>
       <c r="R24" t="n">
-        <v>7073875</v>
+        <v>7074159</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822418</v>
+        <v>119822433</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,21 +3122,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474133</v>
+        <v>474364</v>
       </c>
       <c r="R25" t="n">
-        <v>7074227</v>
+        <v>7073875</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,6 +3182,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822493</v>
+        <v>119822431</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4177,21 +4177,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474372</v>
+        <v>474400</v>
       </c>
       <c r="R35" t="n">
-        <v>7074297</v>
+        <v>7073871</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4237,6 +4237,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4263,7 +4268,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822431</v>
+        <v>119822442</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4303,10 +4308,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474400</v>
+        <v>474435</v>
       </c>
       <c r="R36" t="n">
-        <v>7073871</v>
+        <v>7074155</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4343,7 +4348,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4370,10 +4375,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822442</v>
+        <v>119822493</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4386,21 +4391,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4410,10 +4415,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474435</v>
+        <v>474372</v>
       </c>
       <c r="R37" t="n">
-        <v>7074155</v>
+        <v>7074297</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4446,11 +4451,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5119,10 +5119,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822429</v>
+        <v>119822486</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5135,21 +5135,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474415</v>
+        <v>474121</v>
       </c>
       <c r="R44" t="n">
-        <v>7073880</v>
+        <v>7074098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5195,11 +5195,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5226,10 +5221,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822452</v>
+        <v>119822495</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5242,21 +5237,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5266,10 +5261,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474233</v>
+        <v>474155</v>
       </c>
       <c r="R45" t="n">
-        <v>7074159</v>
+        <v>7074201</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5302,11 +5297,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5333,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822427</v>
+        <v>119822492</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5349,21 +5339,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5363,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474530</v>
+        <v>474448</v>
       </c>
       <c r="R46" t="n">
-        <v>7073855</v>
+        <v>7074194</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5409,11 +5399,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5440,10 +5425,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822495</v>
+        <v>119822429</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5456,21 +5441,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5480,10 +5465,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474155</v>
+        <v>474415</v>
       </c>
       <c r="R47" t="n">
-        <v>7074201</v>
+        <v>7073880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5516,6 +5501,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5542,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119822492</v>
+        <v>119822452</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5558,21 +5548,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5582,10 +5572,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474448</v>
+        <v>474233</v>
       </c>
       <c r="R48" t="n">
-        <v>7074194</v>
+        <v>7074159</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5618,6 +5608,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5644,10 +5639,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119822486</v>
+        <v>119822427</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5660,21 +5655,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5684,10 +5679,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474121</v>
+        <v>474530</v>
       </c>
       <c r="R49" t="n">
-        <v>7074098</v>
+        <v>7073855</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5720,6 +5715,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 26425-2024 artfynd.xlsx
+++ b/artfynd/A 26425-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822420</v>
+        <v>119822454</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474364</v>
+        <v>474182</v>
       </c>
       <c r="R2" t="n">
-        <v>7073718</v>
+        <v>7074153</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822425</v>
+        <v>119822459</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474571</v>
+        <v>474109</v>
       </c>
       <c r="R3" t="n">
-        <v>7073868</v>
+        <v>7074246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822430</v>
+        <v>119822493</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474405</v>
+        <v>474372</v>
       </c>
       <c r="R4" t="n">
-        <v>7073873</v>
+        <v>7074297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822461</v>
+        <v>119822442</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474078</v>
+        <v>474435</v>
       </c>
       <c r="R5" t="n">
-        <v>7074226</v>
+        <v>7074155</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822482</v>
+        <v>119822433</v>
       </c>
       <c r="B6" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474095</v>
+        <v>474364</v>
       </c>
       <c r="R6" t="n">
-        <v>7073945</v>
+        <v>7073875</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822417</v>
+        <v>119822476</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474169</v>
+        <v>474209</v>
       </c>
       <c r="R7" t="n">
-        <v>7074185</v>
+        <v>7073871</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822454</v>
+        <v>119822485</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474182</v>
+        <v>474136</v>
       </c>
       <c r="R8" t="n">
-        <v>7074153</v>
+        <v>7074108</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822455</v>
+        <v>119822461</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474172</v>
+        <v>474078</v>
       </c>
       <c r="R9" t="n">
-        <v>7074172</v>
+        <v>7074226</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822422</v>
+        <v>119822439</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474382</v>
+        <v>474378</v>
       </c>
       <c r="R10" t="n">
-        <v>7073703</v>
+        <v>7074132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822437</v>
+        <v>119822492</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474345</v>
+        <v>474448</v>
       </c>
       <c r="R11" t="n">
-        <v>7074133</v>
+        <v>7074194</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822471</v>
+        <v>119822458</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474127</v>
+        <v>474119</v>
       </c>
       <c r="R12" t="n">
-        <v>7073959</v>
+        <v>7074246</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822469</v>
+        <v>119822431</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474129</v>
+        <v>474400</v>
       </c>
       <c r="R13" t="n">
-        <v>7074044</v>
+        <v>7073871</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822424</v>
+        <v>119822438</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474579</v>
+        <v>474363</v>
       </c>
       <c r="R14" t="n">
-        <v>7073758</v>
+        <v>7074130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822475</v>
+        <v>119822486</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474205</v>
+        <v>474121</v>
       </c>
       <c r="R15" t="n">
-        <v>7073877</v>
+        <v>7074098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2127,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822490</v>
+        <v>119822448</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474005</v>
+        <v>474334</v>
       </c>
       <c r="R16" t="n">
-        <v>7073873</v>
+        <v>7074241</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,6 +2229,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822463</v>
+        <v>119822477</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2305,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474097</v>
+        <v>474098</v>
       </c>
       <c r="R17" t="n">
-        <v>7074133</v>
+        <v>7073885</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822491</v>
+        <v>119822425</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474386</v>
+        <v>474571</v>
       </c>
       <c r="R18" t="n">
-        <v>7074137</v>
+        <v>7073868</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,6 +2443,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822449</v>
+        <v>119822474</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474340</v>
+        <v>474222</v>
       </c>
       <c r="R19" t="n">
-        <v>7074246</v>
+        <v>7073874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822434</v>
+        <v>119822475</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474317</v>
+        <v>474205</v>
       </c>
       <c r="R20" t="n">
-        <v>7073906</v>
+        <v>7073877</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822423</v>
+        <v>119822451</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474482</v>
+        <v>474244</v>
       </c>
       <c r="R21" t="n">
-        <v>7073717</v>
+        <v>7074159</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822489</v>
+        <v>119822428</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474517</v>
+        <v>474418</v>
       </c>
       <c r="R22" t="n">
-        <v>7073863</v>
+        <v>7073882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,6 +2871,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822418</v>
+        <v>119822429</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474133</v>
+        <v>474415</v>
       </c>
       <c r="R23" t="n">
-        <v>7074227</v>
+        <v>7073880</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,6 +2978,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822451</v>
+        <v>119822422</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3039,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474244</v>
+        <v>474382</v>
       </c>
       <c r="R24" t="n">
-        <v>7074159</v>
+        <v>7073703</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,7 +3089,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822433</v>
+        <v>119822446</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3146,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474364</v>
+        <v>474395</v>
       </c>
       <c r="R25" t="n">
-        <v>7073875</v>
+        <v>7074319</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822481</v>
+        <v>119822443</v>
       </c>
       <c r="B26" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474105</v>
+        <v>474450</v>
       </c>
       <c r="R26" t="n">
-        <v>7074062</v>
+        <v>7074166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3289,6 +3299,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3315,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822494</v>
+        <v>119822430</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3331,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3355,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474330</v>
+        <v>474405</v>
       </c>
       <c r="R27" t="n">
-        <v>7074260</v>
+        <v>7073873</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3391,6 +3406,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3417,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822468</v>
+        <v>119822452</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3457,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474149</v>
+        <v>474233</v>
       </c>
       <c r="R28" t="n">
-        <v>7074055</v>
+        <v>7074159</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,7 +3544,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822446</v>
+        <v>119822423</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3564,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474395</v>
+        <v>474482</v>
       </c>
       <c r="R29" t="n">
-        <v>7074319</v>
+        <v>7073717</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3604,7 +3624,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822466</v>
+        <v>119822440</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3671,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474121</v>
+        <v>474401</v>
       </c>
       <c r="R30" t="n">
-        <v>7074052</v>
+        <v>7074148</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3711,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3738,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822453</v>
+        <v>119822495</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3754,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3778,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474191</v>
+        <v>474155</v>
       </c>
       <c r="R31" t="n">
-        <v>7074152</v>
+        <v>7074201</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3814,11 +3834,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822470</v>
+        <v>119822467</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3885,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474150</v>
+        <v>474148</v>
       </c>
       <c r="R32" t="n">
-        <v>7073954</v>
+        <v>7074059</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3952,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822485</v>
+        <v>119822420</v>
       </c>
       <c r="B33" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3968,21 +3983,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474136</v>
+        <v>474364</v>
       </c>
       <c r="R33" t="n">
-        <v>7074108</v>
+        <v>7073718</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4028,6 +4043,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4054,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822477</v>
+        <v>119822482</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,21 +4090,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4094,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474098</v>
+        <v>474095</v>
       </c>
       <c r="R34" t="n">
-        <v>7073885</v>
+        <v>7073945</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4130,11 +4150,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4161,7 +4176,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822431</v>
+        <v>119822419</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4201,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474400</v>
+        <v>474170</v>
       </c>
       <c r="R35" t="n">
-        <v>7073871</v>
+        <v>7073676</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4241,7 +4256,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822442</v>
+        <v>119822489</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4284,21 +4299,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4308,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474435</v>
+        <v>474517</v>
       </c>
       <c r="R36" t="n">
-        <v>7074155</v>
+        <v>7073863</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4344,11 +4359,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822493</v>
+        <v>119822490</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4391,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4415,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474372</v>
+        <v>474005</v>
       </c>
       <c r="R37" t="n">
-        <v>7074297</v>
+        <v>7073873</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4477,7 +4487,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822458</v>
+        <v>119822450</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4517,10 +4527,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474119</v>
+        <v>474273</v>
       </c>
       <c r="R38" t="n">
-        <v>7074246</v>
+        <v>7074232</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4557,7 +4567,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4584,7 +4594,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822436</v>
+        <v>119822427</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4624,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474298</v>
+        <v>474530</v>
       </c>
       <c r="R39" t="n">
-        <v>7074026</v>
+        <v>7073855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4664,7 +4674,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4691,7 +4701,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822428</v>
+        <v>119822470</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4731,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474418</v>
+        <v>474150</v>
       </c>
       <c r="R40" t="n">
-        <v>7073882</v>
+        <v>7073954</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4771,7 +4781,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4798,7 +4808,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822464</v>
+        <v>119822478</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4838,10 +4848,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474094</v>
+        <v>474080</v>
       </c>
       <c r="R41" t="n">
-        <v>7074062</v>
+        <v>7073873</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4878,7 +4888,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4905,7 +4915,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822447</v>
+        <v>119822468</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4945,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474350</v>
+        <v>474149</v>
       </c>
       <c r="R42" t="n">
-        <v>7074246</v>
+        <v>7074055</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5012,7 +5022,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822440</v>
+        <v>119822462</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5052,10 +5062,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474401</v>
+        <v>474099</v>
       </c>
       <c r="R43" t="n">
-        <v>7074148</v>
+        <v>7074178</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5092,7 +5102,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5119,10 +5129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822486</v>
+        <v>119822418</v>
       </c>
       <c r="B44" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5135,21 +5145,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5159,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474121</v>
+        <v>474133</v>
       </c>
       <c r="R44" t="n">
-        <v>7074098</v>
+        <v>7074227</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5221,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822495</v>
+        <v>119822488</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5237,21 +5247,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5261,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474155</v>
+        <v>474121</v>
       </c>
       <c r="R45" t="n">
-        <v>7074201</v>
+        <v>7073951</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5323,10 +5333,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822492</v>
+        <v>119822445</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5339,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5363,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474448</v>
+        <v>474457</v>
       </c>
       <c r="R46" t="n">
-        <v>7074194</v>
+        <v>7074300</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5399,6 +5409,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5425,10 +5440,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822429</v>
+        <v>119822491</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5441,21 +5456,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5465,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474415</v>
+        <v>474386</v>
       </c>
       <c r="R47" t="n">
-        <v>7073880</v>
+        <v>7074137</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5501,11 +5516,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5532,7 +5542,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119822452</v>
+        <v>119822460</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5572,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474233</v>
+        <v>474092</v>
       </c>
       <c r="R48" t="n">
-        <v>7074159</v>
+        <v>7074245</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5639,7 +5649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119822427</v>
+        <v>119822436</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5679,10 +5689,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474530</v>
+        <v>474298</v>
       </c>
       <c r="R49" t="n">
-        <v>7073855</v>
+        <v>7074026</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5719,7 +5729,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5746,10 +5756,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119822488</v>
+        <v>119822441</v>
       </c>
       <c r="B50" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5762,21 +5772,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5786,10 +5796,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474121</v>
+        <v>474422</v>
       </c>
       <c r="R50" t="n">
-        <v>7073951</v>
+        <v>7074145</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5822,6 +5832,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5848,7 +5863,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119822460</v>
+        <v>119822466</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5888,10 +5903,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474092</v>
+        <v>474121</v>
       </c>
       <c r="R51" t="n">
-        <v>7074245</v>
+        <v>7074052</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5928,7 +5943,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5955,7 +5970,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119822438</v>
+        <v>119822444</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -5995,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474363</v>
+        <v>474438</v>
       </c>
       <c r="R52" t="n">
-        <v>7074130</v>
+        <v>7074241</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6035,7 +6050,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6062,7 +6077,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119822448</v>
+        <v>119822449</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6102,10 +6117,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474334</v>
+        <v>474340</v>
       </c>
       <c r="R53" t="n">
-        <v>7074241</v>
+        <v>7074246</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6142,7 +6157,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6169,7 +6184,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119822456</v>
+        <v>119822434</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6209,10 +6224,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474160</v>
+        <v>474317</v>
       </c>
       <c r="R54" t="n">
-        <v>7074200</v>
+        <v>7073906</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6276,7 +6291,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119822419</v>
+        <v>119822469</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6316,10 +6331,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474170</v>
+        <v>474129</v>
       </c>
       <c r="R55" t="n">
-        <v>7073676</v>
+        <v>7074044</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6356,7 +6371,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6383,7 +6398,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119822462</v>
+        <v>119822464</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6423,10 +6438,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474099</v>
+        <v>474094</v>
       </c>
       <c r="R56" t="n">
-        <v>7074178</v>
+        <v>7074062</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6463,7 +6478,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6490,7 +6505,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119822439</v>
+        <v>119822455</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6530,10 +6545,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474378</v>
+        <v>474172</v>
       </c>
       <c r="R57" t="n">
-        <v>7074132</v>
+        <v>7074172</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6570,7 +6585,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6597,10 +6612,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119822467</v>
+        <v>119822417</v>
       </c>
       <c r="B58" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6613,21 +6628,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6637,10 +6652,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474148</v>
+        <v>474169</v>
       </c>
       <c r="R58" t="n">
-        <v>7074059</v>
+        <v>7074185</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6673,11 +6688,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6704,10 +6714,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119822457</v>
+        <v>119822481</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6720,21 +6730,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6744,10 +6754,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474128</v>
+        <v>474105</v>
       </c>
       <c r="R59" t="n">
-        <v>7074233</v>
+        <v>7074062</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6780,11 +6790,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6811,7 +6816,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119822474</v>
+        <v>119822456</v>
       </c>
       <c r="B60" t="n">
         <v>57320</v>
@@ -6851,10 +6856,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474222</v>
+        <v>474160</v>
       </c>
       <c r="R60" t="n">
-        <v>7073874</v>
+        <v>7074200</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,7 +6896,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6918,7 +6923,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119822478</v>
+        <v>119822457</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -6958,10 +6963,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474080</v>
+        <v>474128</v>
       </c>
       <c r="R61" t="n">
-        <v>7073873</v>
+        <v>7074233</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7025,10 +7030,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119822484</v>
+        <v>119822437</v>
       </c>
       <c r="B62" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7041,21 +7046,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7065,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474078</v>
+        <v>474345</v>
       </c>
       <c r="R62" t="n">
-        <v>7074201</v>
+        <v>7074133</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7101,6 +7106,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7127,10 +7137,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119822480</v>
+        <v>119822424</v>
       </c>
       <c r="B63" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7143,21 +7153,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7167,10 +7177,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474098</v>
+        <v>474579</v>
       </c>
       <c r="R63" t="n">
-        <v>7074059</v>
+        <v>7073758</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7203,6 +7213,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7229,10 +7244,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119822445</v>
+        <v>119822480</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7245,21 +7260,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7269,10 +7284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474457</v>
+        <v>474098</v>
       </c>
       <c r="R64" t="n">
-        <v>7074300</v>
+        <v>7074059</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7305,11 +7320,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7336,7 +7346,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119822441</v>
+        <v>119822463</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7376,10 +7386,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474422</v>
+        <v>474097</v>
       </c>
       <c r="R65" t="n">
-        <v>7074145</v>
+        <v>7074133</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7443,7 +7453,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119822476</v>
+        <v>119822471</v>
       </c>
       <c r="B66" t="n">
         <v>57320</v>
@@ -7483,10 +7493,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474209</v>
+        <v>474127</v>
       </c>
       <c r="R66" t="n">
-        <v>7073871</v>
+        <v>7073959</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7523,7 +7533,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7550,7 +7560,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119822443</v>
+        <v>119822432</v>
       </c>
       <c r="B67" t="n">
         <v>57320</v>
@@ -7590,10 +7600,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474450</v>
+        <v>474397</v>
       </c>
       <c r="R67" t="n">
-        <v>7074166</v>
+        <v>7073871</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7630,7 +7640,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7657,7 +7667,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119822444</v>
+        <v>119822453</v>
       </c>
       <c r="B68" t="n">
         <v>57320</v>
@@ -7697,10 +7707,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474438</v>
+        <v>474191</v>
       </c>
       <c r="R68" t="n">
-        <v>7074241</v>
+        <v>7074152</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7737,7 +7747,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7764,7 +7774,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119822450</v>
+        <v>119822447</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -7804,10 +7814,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474273</v>
+        <v>474350</v>
       </c>
       <c r="R69" t="n">
-        <v>7074232</v>
+        <v>7074246</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7844,7 +7854,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7871,10 +7881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119822432</v>
+        <v>119822494</v>
       </c>
       <c r="B70" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7887,21 +7897,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7911,10 +7921,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474397</v>
+        <v>474330</v>
       </c>
       <c r="R70" t="n">
-        <v>7073871</v>
+        <v>7074260</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7947,11 +7957,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7978,10 +7983,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119822459</v>
+        <v>119822484</v>
       </c>
       <c r="B71" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7994,21 +7999,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8018,10 +8023,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474109</v>
+        <v>474078</v>
       </c>
       <c r="R71" t="n">
-        <v>7074246</v>
+        <v>7074201</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8054,11 +8059,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
